--- a/workspaces/btc_daily_14days/rsi/rsi_14.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_14.xlsx
@@ -575,46 +575,46 @@
         <v>41</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.92119582613149</v>
+        <v>10.88881243863646</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.75154664949606</v>
+        <v>11.71674609647915</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.35940389511462</v>
+        <v>11.32564790531084</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.051775647975944</v>
+        <v>9.024699612785824</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.07365790522676</v>
+        <v>6.055367291133784</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.488775630804184</v>
+        <v>1.484404175490631</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-5.923718496400063</v>
+        <v>-5.905986897425841</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.950007132703703</v>
+        <v>-3.938014971700994</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.875373062947105</v>
+        <v>0.873369251807766</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.421140073433534</v>
+        <v>-2.413103157412067</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.517200882166676</v>
+        <v>-7.494057213035155</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-9.930319625862552</v>
+        <v>-9.900031733053495</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-15.24684944859558</v>
+        <v>-15.20085911555344</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-17.44266929787837</v>
+        <v>-17.39016217352105</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>53</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.883920170356916</v>
+        <v>7.859889688448618</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.499416254939341</v>
+        <v>2.491561016440102</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.880495954112803</v>
+        <v>5.862387334213317</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.78879691351937</v>
+        <v>9.758872815692534</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.474951095475944</v>
+        <v>5.458027114038885</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.663128283911291</v>
+        <v>7.64012638382772</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.469624484979484</v>
+        <v>9.441581303889983</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>12.78413661499236</v>
+        <v>12.74619567725809</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.94493003418436</v>
+        <v>8.91866439711314</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.203743439143132</v>
+        <v>6.186088149101565</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.108287448570834</v>
+        <v>4.097089943642516</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.035632636110286</v>
+        <v>6.018722638142258</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.507879527639439</v>
+        <v>7.486669646524668</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.758271355858852</v>
+        <v>7.736390978800955</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.35271552594299</v>
+        <v>1.4118677504174</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.358936452965494</v>
+        <v>9.714352133046027</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.89037171118662</v>
+        <v>11.30604160926566</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.249987329236447</v>
+        <v>5.457944994344018</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.56241005687005</v>
+        <v>8.891302165588002</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.085741429797366</v>
+        <v>3.20492066698219</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.8504800791233933</v>
+        <v>-0.88227242840005</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.318660363270425</v>
+        <v>-1.366913898845446</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.473643786717176</v>
+        <v>2.563235696007141</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.233139290345385</v>
+        <v>-2.325628336141641</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.416665472691832</v>
+        <v>1.457371080685299</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.314140896929018</v>
+        <v>-1.375413321303398</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.228038973513044</v>
+        <v>3.335726250299111</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.541668006794573</v>
+        <v>1.585447582574481</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.317372490600839</v>
+        <v>8.414566287955061</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.355902278235142</v>
+        <v>5.419811723493972</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.37053613763078</v>
+        <v>10.49248807945364</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.798876850300438</v>
+        <v>7.891750915744254</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.556483973893656</v>
+        <v>4.612202706766745</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.208407325282252</v>
+        <v>6.280483982445105</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.418044845931313</v>
+        <v>3.456684360650463</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.950936190698307</v>
+        <v>2.984524859982706</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1821663708972423</v>
+        <v>0.1837300703120732</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.393056743707469</v>
+        <v>3.428427737761908</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.46372928753739</v>
+        <v>-1.483881748155596</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.429346130191959</v>
+        <v>-1.449498590810165</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4908286052612709</v>
+        <v>-0.4998901880570514</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2433863274000743</v>
+        <v>-0.2501688557795205</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>136</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-10.58167361432762</v>
+        <v>-10.55718858709413</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.370516454217558</v>
+        <v>-3.363328706005255</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.55922494075682</v>
+        <v>-1.556881468672515</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.04260919280072528</v>
+        <v>0.04119321055597425</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.711911897419746</v>
+        <v>1.706706385548237</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.9350296304997414</v>
+        <v>-0.933421448912803</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.020422372360294</v>
+        <v>-1.018093684155332</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.382108966534993</v>
+        <v>-7.36449119265216</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.497947891473444</v>
+        <v>-4.487014891312946</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-8.300038921306999</v>
+        <v>-8.27953132472468</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.083189038658411</v>
+        <v>-4.072519943160913</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.785875118879289</v>
+        <v>-4.773430903462206</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.418212139294198</v>
+        <v>-7.399567867347614</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.956783267593032</v>
+        <v>-4.94396418213082</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.9949337728132761</v>
+        <v>1.000734123567035</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.942960030184821</v>
+        <v>-2.95782827321969</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.114259077736122</v>
+        <v>-4.13413590820992</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.433194945445344</v>
+        <v>-2.443605838751985</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.420666066782594</v>
+        <v>-1.425644174560148</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.004802668196589</v>
+        <v>-5.031363580615754</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.985433476499963</v>
+        <v>-1.996405858883087</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.677793825715476</v>
+        <v>-1.688264627940448</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.847133139528033</v>
+        <v>-4.875323867206582</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.929380489308173</v>
+        <v>-2.948648971784195</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.686925176702466</v>
+        <v>-4.715902296101063</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.562938382694028</v>
+        <v>1.568480861243835</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.516285482963447</v>
+        <v>-3.5392737497016</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.04511730709666</v>
+        <v>-4.070802417424602</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>123</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.273926125088025</v>
+        <v>-1.271190294938542</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.326000144322329</v>
+        <v>-5.314192016111647</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.535908894590285</v>
+        <v>-6.52187717612545</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.33868998367889</v>
+        <v>-2.334469179095976</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.702988223424647</v>
+        <v>7.684166364624325</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.374252575974694</v>
+        <v>6.359453208939215</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.84777988468128</v>
+        <v>3.839066523854783</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.565671422675209</v>
+        <v>2.560393608416447</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.69003515613894</v>
+        <v>1.687045318935141</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.8373534888300611</v>
+        <v>0.8369201339070287</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6320249559999169</v>
+        <v>0.6321668095896342</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.296612951487603</v>
+        <v>2.292566227097666</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.134403270718856</v>
+        <v>5.12434413647815</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>7.014521177308509</v>
+        <v>7.000081728916676</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.655449493394336</v>
+        <v>-1.661085111334593</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.591526696640116</v>
+        <v>-1.597077223341053</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.781977564920957</v>
+        <v>-4.797936273299484</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.975284523638358</v>
+        <v>-2.984146491012453</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1586867697653673</v>
+        <v>-0.1564994005835771</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-3.218372094542119</v>
+        <v>-3.228552563340045</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.185191163478258</v>
+        <v>-2.192528797185346</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.943875499161521</v>
+        <v>2.9534991269961</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.193493114037651</v>
+        <v>3.203442505378916</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.347367458501125</v>
+        <v>2.353317320350989</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.6557090306409208</v>
+        <v>-0.6604247680116586</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.182070379222594</v>
+        <v>-1.187839363474964</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.279959049035185</v>
+        <v>-3.293487232846829</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2322145166464793</v>
+        <v>-0.2347771365257216</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>159</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.694696181845337</v>
+        <v>-4.68414815230873</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.050040078374778</v>
+        <v>-5.038616646877337</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.558771570969483</v>
+        <v>-3.55076651932162</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.206402297464315</v>
+        <v>-7.191034705001371</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-7.117311278894825</v>
+        <v>-7.10330306260223</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.932683282336704</v>
+        <v>-4.92202775771964</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-9.430362233407642</v>
+        <v>-9.409314867277473</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-6.119612352683141</v>
+        <v>-6.105920126988707</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.181085263889329</v>
+        <v>-6.166920013171008</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-5.142914771010844</v>
+        <v>-5.130252745368743</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.718281252695014</v>
+        <v>-4.706075252076118</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.944023280684753</v>
+        <v>-5.929553729950953</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-6.365764541705055</v>
+        <v>-6.349808340895855</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-9.896891790457587</v>
+        <v>-9.873671914279946</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>167</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>8.584405991167543</v>
+        <v>8.564915410777083</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.777050395491912</v>
+        <v>5.764290741536726</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.987005075591412</v>
+        <v>2.980509862242691</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.320272543090319</v>
+        <v>1.317292186311221</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.981511631362487</v>
+        <v>1.975679216158433</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>7.677556726595427</v>
+        <v>7.659756553548682</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.194330540831963</v>
+        <v>5.183327098888057</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.329280243328832</v>
+        <v>8.310529991641957</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7.067330883549573</v>
+        <v>7.051925315040627</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.614218969504648</v>
+        <v>5.602997734803118</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>7.209127711786728</v>
+        <v>7.194651596114149</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.443323908635762</v>
+        <v>5.432627567830835</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.021419631159461</v>
+        <v>5.012372956886068</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.129944811949791</v>
+        <v>-0.1271272677238713</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>195</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.749848576620344</v>
+        <v>-2.74338433048522</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-7.441031696035417</v>
+        <v>-7.422226689341016</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-9.378458564561086</v>
+        <v>-9.354717879076858</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-12.84498144884966</v>
+        <v>-12.81274532850477</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-12.87433760380767</v>
+        <v>-12.84358847131265</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-12.5813291077601</v>
+        <v>-12.55052298342869</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-13.18581968241706</v>
+        <v>-13.1520555101493</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-16.22870310984629</v>
+        <v>-16.18816492621452</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-14.23401493225049</v>
+        <v>-14.197882761115</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-14.57324813138355</v>
+        <v>-14.53518743332241</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-14.26473629941759</v>
+        <v>-14.22712024481937</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-16.28654974236213</v>
+        <v>-16.24401913875599</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-15.16633083577456</v>
+        <v>-15.12581221123946</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-11.3176509713723</v>
+        <v>-11.28634728921947</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-7.998025476173275</v>
+        <v>-8.056373597720977</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.401303522858228</v>
+        <v>-6.45210829546771</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.749517570530273</v>
+        <v>-1.767589277356869</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7017494193226312</v>
+        <v>-0.7132740879175969</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.456614187939721</v>
+        <v>-4.490693603295512</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2304028146664407</v>
+        <v>-0.2359726642703066</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.692311405958399</v>
+        <v>-1.713319257806155</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.577304417292275</v>
+        <v>-5.625486863536679</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.556222748476834</v>
+        <v>-6.612412675644805</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.017871726724842</v>
+        <v>-6.07364897178374</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.003003498234875</v>
+        <v>-3.037661555360671</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.589527222063403</v>
+        <v>-1.614389509126362</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.2932244814571519</v>
+        <v>0.2801706947435534</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.297843261580191</v>
+        <v>-1.321959824832007</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-7.744579872721395</v>
+        <v>-7.768811214138438</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.508399104565797</v>
+        <v>-2.518937323893304</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.650091300363961</v>
+        <v>-2.660411862324494</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.720649491145913</v>
+        <v>-5.740012691654954</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.261485456581177</v>
+        <v>-6.281254350985485</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-7.793891965404072</v>
+        <v>-7.818025447559855</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.592568725077946</v>
+        <v>-5.612771694452661</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.39875955405909</v>
+        <v>-2.410230322591964</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.458975965495313</v>
+        <v>-2.471230208774266</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.018294595267932</v>
+        <v>-1.027777412150812</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7654238483602853</v>
+        <v>-0.7738151401381188</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.475665868727617</v>
+        <v>-3.491725560774341</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.607352423692198</v>
+        <v>-1.618402190067762</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.102592044020057</v>
+        <v>-4.120974435773228</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.751844698657955</v>
+        <v>1.752791452018364</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-5.995312437418093</v>
+        <v>-6.020251191545029</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-8.2779371672382</v>
+        <v>-8.309725947856904</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-8.624522066048165</v>
+        <v>-8.658686307813717</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-7.750884708917546</v>
+        <v>-7.780854631753606</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-10.28737211568814</v>
+        <v>-10.3262061741661</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-10.57735866498754</v>
+        <v>-10.61951111790596</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-13.40521764384369</v>
+        <v>-13.45636276313285</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.269249949113053</v>
+        <v>-8.304092507134953</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-7.69818652997872</v>
+        <v>-7.732416744295797</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.902798337843286</v>
+        <v>-7.93717006861327</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.033679860644902</v>
+        <v>-5.059185015533245</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.980299281171206</v>
+        <v>-5.005505977189152</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.258074890101625</v>
+        <v>-4.28185099562365</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.136630808472887</v>
+        <v>-4.157105248485664</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-5.953149941552532</v>
+        <v>-5.983241310946454</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.468325186834598</v>
+        <v>-4.492890196218596</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.809995078722579</v>
+        <v>-4.837423044130475</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.59242790272679</v>
+        <v>-1.606161929782658</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.354698199977399</v>
+        <v>-0.3653237656519011</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.4361729681490019</v>
+        <v>-0.4500574829240804</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.841071277411189</v>
+        <v>-1.860637108120777</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.312674334780993</v>
+        <v>-3.336731333925833</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.338505751970267</v>
+        <v>-1.356667839708159</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.483032270410959</v>
+        <v>-2.504817390440934</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.509047442579416</v>
+        <v>-1.527038006680627</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.807819299949237</v>
+        <v>-3.834085070455608</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.55809796767295</v>
+        <v>-3.58436373817932</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>218</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>5.763442413734971</v>
+        <v>5.759094380038043</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.775722011780054</v>
+        <v>2.776160200902154</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.08727532353192657</v>
+        <v>0.09064792473851213</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.215609885939557</v>
+        <v>0.2194470263392034</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.539058622480255</v>
+        <v>-3.531901933244718</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.9453451294412503</v>
+        <v>-0.9408820138776264</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.868257650800395</v>
+        <v>-2.860478116471064</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.040086515175531</v>
+        <v>-1.034083533601134</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.27673766656401</v>
+        <v>0.2810633692073878</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.493118835149232</v>
+        <v>-1.48649300848119</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7795469415208984</v>
+        <v>-0.7738151401382183</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.204173556328804</v>
+        <v>-1.198147579122747</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.6711097713159475</v>
+        <v>0.6751757915834133</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9161861406662837</v>
+        <v>-0.9099652614613021</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-5.018690845462501</v>
+        <v>-5.047798198987593</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4404426122802505</v>
+        <v>0.428288208982103</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.0455739056837885</v>
+        <v>0.03109206345607873</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.700280134050544</v>
+        <v>2.694968188840008</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.081437852043223</v>
+        <v>-1.100942123250661</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.236258684163658</v>
+        <v>1.226956667256765</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.178997166347486</v>
+        <v>3.172679802776479</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1874621624381945</v>
+        <v>0.1674253380050672</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.8853405374994452</v>
+        <v>-0.9088029745732271</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.235180614292361</v>
+        <v>-2.266542372799073</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.603410744465911</v>
+        <v>1.589618008467106</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.3845228683841881</v>
+        <v>-0.4064556869794487</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.308358943039345</v>
+        <v>-1.334324511122098</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9639369308953292</v>
+        <v>0.9458536739459618</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.385330212101863</v>
+        <v>-4.422479605804732</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.834741662903966</v>
+        <v>-3.874926246090837</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.6352544953642507</v>
+        <v>0.6182636722801789</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.865145114063452</v>
+        <v>4.86950292761928</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.328877446961712</v>
+        <v>4.331081712547181</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.8393052789381201</v>
+        <v>0.8241758241758816</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.004634373481544</v>
+        <v>4.000311672120873</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.92121322300418</v>
+        <v>1.902693490730734</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.318954946957966</v>
+        <v>1.298215343678997</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.179787731852059</v>
+        <v>3.165481462998763</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.513062475443057</v>
+        <v>3.504206399550753</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3045613142069641</v>
+        <v>0.2777199916787936</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.589880803258445</v>
+        <v>2.574856685081713</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.299061594994185</v>
+        <v>2.281099756488445</v>
       </c>
     </row>
     <row r="24">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 17.89</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4081~4093</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4081</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.01359468473477676</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 20.37</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4040~4052</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4040</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.1242379253432446</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 22.85</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3987~3999</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3987</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.230372553768369</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 25.33</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3937~3947</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3937</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.2512290473445091</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 27.81</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3864~3873</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3864</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.4149461952422513</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 30.29</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3728~3737</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3728</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.04495022815752492</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 32.76</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3600~3608</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3600</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.08213011621884192</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 35.24</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3477~3485</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3477</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.04006672767052066</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 37.72</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3299~3306</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3299</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.04739652552505191</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 40.2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3140~3147</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3140</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.2869874821414768</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 42.68</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2973~2980</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2973</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.178002078599242</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 45.16</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2778~2785</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2778</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.002073349448913575</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 47.64</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2562~2567</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2562</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.681474028835602</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 50.11</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2344~2348</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2344</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.467379396996158</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 52.59</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2133~2136</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2133</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.439145949452943</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 55.07</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1921~1923</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1921</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>2.056743687070316</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 57.55</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1703~1705</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1703</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.582808014100877</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 60.03</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1506~1507</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1506</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>2.450158229225991</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 62.51</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1322~1322</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1322</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>3.406712965720438</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 64.99</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1141~1141</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1141</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>3.948279471201062</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 67.46</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>977~977</t>
-        </is>
+      <c r="B26" t="n">
+        <v>977</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>3.698987473034649</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 69.94</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>844~844</t>
-        </is>
+      <c r="B27" t="n">
+        <v>844</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>4.734049831448793</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 72.42</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>711~711</t>
-        </is>
+      <c r="B28" t="n">
+        <v>711</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>5.734409781055845</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 74.9</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>608~608</t>
-        </is>
+      <c r="B29" t="n">
+        <v>608</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>5.401298521895292</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 77.38</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>494~494</t>
-        </is>
+      <c r="B30" t="n">
+        <v>494</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>6.615873420680714</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 79.86</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>387~387</t>
-        </is>
+      <c r="B31" t="n">
+        <v>387</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>4.870902765061345</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 82.34</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>289~289</t>
-        </is>
+      <c r="B32" t="n">
+        <v>289</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>4.599987285326357</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 84.82</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>189~189</t>
-        </is>
+      <c r="B33" t="n">
+        <v>189</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>2.53301670624505</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 87.29</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>127~127</t>
-        </is>
+      <c r="B34" t="n">
+        <v>127</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>6.56167979002624</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 89.77</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>5.83989501312336</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 17.89</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>83~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1.077990251218594</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 20.37</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>124~125</t>
-        </is>
+      <c r="B7" t="n">
+        <v>124</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>4.306561679790022</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 22.85</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>177~178</t>
-        </is>
+      <c r="B8" t="n">
+        <v>177</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>5.371730219115861</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 25.33</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>227~230</t>
-        </is>
+      <c r="B9" t="n">
+        <v>227</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>4.463083418920462</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 27.81</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>300~304</t>
-        </is>
+      <c r="B10" t="n">
+        <v>300</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>5.401298521895292</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 30.29</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>436~440</t>
-        </is>
+      <c r="B11" t="n">
+        <v>436</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.461107134335478</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 32.76</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>564~569</t>
-        </is>
+      <c r="B12" t="n">
+        <v>564</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.5821328572944111</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 35.24</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>687~692</t>
-        </is>
+      <c r="B13" t="n">
+        <v>687</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.2522264196744146</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 37.72</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>865~871</t>
-        </is>
+      <c r="B14" t="n">
+        <v>865</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.1398217874889625</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 40.2</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1024~1030</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1024</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.8429528833167765</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 42.68</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1191~1197</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1191</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.4723093823798266</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 45.16</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1386~1392</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1386</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.02092949588197968</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 47.64</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1602~1610</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1602</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.064866891638552</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 50.11</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1820~1829</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1820</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.864679435573557</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 52.59</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2031~2041</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2031</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.489028717074262</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 55.07</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2243~2254</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2243</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-1.73922359083997</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 57.55</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2461~2472</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2461</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.077580715031978</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 60.03</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2658~2670</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2658</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-1.369842814591998</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 62.51</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2842~2855</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2842</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-1.565242173099648</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 64.99</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3023~3036</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3023</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-1.472357951303515</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 67.46</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3187~3200</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3187</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-1.118438320209968</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 69.94</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3320~3333</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3320</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-1.188307807158672</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 72.42</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3453~3466</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3453</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.166260016690067</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 74.9</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3556~3569</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3556</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.9103618281954056</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 77.38</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3670~3683</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3670</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.8779075029414471</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 79.86</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3777~3790</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3777</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.4881612753550968</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 82.34</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3875~3888</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3875</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.3329444930494816</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 84.82</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3975~3988</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3975</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.1112918808920185</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 87.29</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4037~4050</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4037</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.1971420239136776</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 89.77</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4080~4093</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4080</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.1113225127337927</v>

--- a/workspaces/btc_daily_14days/rsi/rsi_14.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>41</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.88881243863646</v>
+        <v>10.89860365244412</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.71674609647915</v>
+        <v>11.72672530023624</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.32564790531084</v>
+        <v>11.33581353657102</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.024699612785824</v>
+        <v>9.035395230024193</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.055367291133784</v>
+        <v>6.066927480752319</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.484404175490631</v>
+        <v>1.497057103396102</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-5.905986897425841</v>
+        <v>-5.891468734819611</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.938014971700994</v>
+        <v>-3.923856149107287</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.873369251807766</v>
+        <v>0.8863844466006157</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.413103157412067</v>
+        <v>-2.399042597446766</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.494057213035155</v>
+        <v>-7.478682990643925</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-9.900031733053495</v>
+        <v>-9.884063554145435</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-15.20085911555344</v>
+        <v>-15.18347494215332</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-17.39016217352105</v>
+        <v>-17.4005918092192</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>53</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.859889688448618</v>
+        <v>7.870373952659456</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.491561016440102</v>
+        <v>2.503778206725087</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.862387334213317</v>
+        <v>5.873852655206363</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.758872815692534</v>
+        <v>9.769331048749116</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.458027114038885</v>
+        <v>5.46970031226536</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.64012638382772</v>
+        <v>7.651229279384495</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.441581303889983</v>
+        <v>9.452290981566307</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>12.74619567725809</v>
+        <v>12.75619915394632</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.91866439711314</v>
+        <v>8.929659915477643</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.186088149101565</v>
+        <v>6.198009500684833</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.097089943642516</v>
+        <v>4.109604277345532</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.018722638142258</v>
+        <v>6.030759440592881</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.486669646524668</v>
+        <v>7.498455102569622</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.736390978800955</v>
+        <v>7.725961343102803</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.4118677504174</v>
+        <v>1.424458842819696</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.714352133046027</v>
+        <v>9.725266077079077</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.30604160926566</v>
+        <v>11.31663493618775</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.457944994344018</v>
+        <v>5.469973058844282</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.891302165588002</v>
+        <v>8.902619781826324</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.20492066698219</v>
+        <v>3.217648571427219</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.88227242840005</v>
+        <v>-0.868452550968108</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.366913898845446</v>
+        <v>-1.352855216481892</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.563235696007141</v>
+        <v>2.576346264367288</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.325628336141641</v>
+        <v>-2.311014348393627</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.457371080685299</v>
+        <v>1.471105128013491</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-1.375413321303398</v>
+        <v>-2.4927879580829</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>2.209362537372513</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.585447582574481</v>
+        <v>1.575017946876329</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>73</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.414566287955061</v>
+        <v>8.424998308937603</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.419811723493972</v>
+        <v>5.431404968656388</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.49248807945364</v>
+        <v>10.50284619283949</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.891750915744254</v>
+        <v>7.902753268602062</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.612202706766745</v>
+        <v>4.624197558721235</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.280483982445105</v>
+        <v>6.292037017487914</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.456684360650463</v>
+        <v>3.469035509449704</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.984524859982706</v>
+        <v>2.997112127737701</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1837300703120732</v>
+        <v>0.1970775458587894</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.428427737761908</v>
+        <v>3.44120911818473</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.483881748155596</v>
+        <v>-2.245451065547357</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.449498590810165</v>
+        <v>-1.436046302090055</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4998901880570514</v>
+        <v>-0.4863341417054485</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2501688557795205</v>
+        <v>-0.2605984914776727</v>
       </c>
     </row>
     <row r="10">
@@ -783,150 +783,150 @@
         <v>136</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-10.55718858709413</v>
+        <v>-10.54198898024576</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.363328706005255</v>
+        <v>-3.349655585248883</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.556881468672515</v>
+        <v>-1.543644324878869</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.04119321055597425</v>
+        <v>0.05398925716937697</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.706706385548237</v>
+        <v>1.719217117479758</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.933421448912803</v>
+        <v>-0.9202189181730915</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.018093684155332</v>
+        <v>-1.004784105137489</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.36449119265216</v>
+        <v>-7.349365683098043</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.487014891312946</v>
+        <v>-4.472609690898899</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-8.27953132472468</v>
+        <v>-8.263852091816915</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.072519943160913</v>
+        <v>-4.059062649450695</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.773430903462206</v>
+        <v>-4.759978614742096</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.399567867347614</v>
+        <v>-7.386011820996011</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.94396418213082</v>
+        <v>-4.954393817828972</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 31.52</t>
+          <t>X ≈ 31.53</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>128</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.000734123567035</v>
+        <v>1.013041024393679</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.95782827321969</v>
+        <v>-2.944095204415916</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.13413590820992</v>
+        <v>-4.120050751448836</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.443605838751985</v>
+        <v>-2.43001782708474</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.425644174560148</v>
+        <v>-1.412191003982443</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.031363580615754</v>
+        <v>-5.016894561677411</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.996405858883087</v>
+        <v>-1.982688425387245</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.688264627940448</v>
+        <v>-1.674451935347008</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.875323867206582</v>
+        <v>-4.860601855032968</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.948648971784195</v>
+        <v>-3.37730270709703</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.715902296101063</v>
+        <v>-4.702445002390846</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.568480861243835</v>
+        <v>1.581933149963945</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.5392737497016</v>
+        <v>-3.525717703349997</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.070802417424602</v>
+        <v>-4.081232053122754</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 34</t>
+          <t>X ≈ 34.01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.271190294938542</v>
+        <v>-2.075757858226822</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.314192016111647</v>
+        <v>-5.280369749755721</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.52187717612545</v>
+        <v>-6.474687744727873</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.334469179095976</v>
+        <v>-2.353451547815396</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.684166364624325</v>
+        <v>7.49356304663641</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.359453208939215</v>
+        <v>6.195218810822787</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.839066523854783</v>
+        <v>3.714562009815403</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.560393608416447</v>
+        <v>2.449399506810678</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.687045318935141</v>
+        <v>1.589328481505703</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.8369201339070287</v>
+        <v>0.7397561558689887</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6321668095896342</v>
+        <v>-0.2649450023913857</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.292566227097666</v>
+        <v>2.169433149964306</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.12434413647815</v>
+        <v>4.949282296651255</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>7.000081728916676</v>
+        <v>6.775017946877249</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.661085111334593</v>
+        <v>-1.07191754872791</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.597077223341053</v>
+        <v>-1.555231692333876</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.797936273299484</v>
+        <v>-4.786949380407954</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.984146491012453</v>
+        <v>-2.954655589513962</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.1564994005835771</v>
+        <v>-0.08958424845006618</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-3.228552563340045</v>
+        <v>-3.198889486374725</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.192528797185346</v>
+        <v>-2.150340427146581</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.9534991269961</v>
+        <v>3.058109951131371</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>3.203442505378916</v>
+        <v>2.996763821327441</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.353317320350989</v>
+        <v>2.462483428596137</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.6604247680116586</v>
+        <v>-0.014945002391201</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.187839363474964</v>
+        <v>-1.116930486399511</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.293487232846829</v>
+        <v>-3.241626794258501</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2347771365257216</v>
+        <v>-0.1749820531228892</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>159</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.68414815230873</v>
+        <v>-4.67016320616294</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.038616646877337</v>
+        <v>-5.024115008954638</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.55076651932162</v>
+        <v>-3.536649462943409</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.191034705001371</v>
+        <v>-7.175889701002177</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-7.10330306260223</v>
+        <v>-7.088214464522906</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.92202775771964</v>
+        <v>-4.907479841630284</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-9.409314867277473</v>
+        <v>-9.39325431345555</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-6.105920126988707</v>
+        <v>-6.090789033514106</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.166920013171008</v>
+        <v>-6.153721274216245</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-5.130252745368743</v>
+        <v>-5.116847617715912</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.706075252076118</v>
+        <v>-4.692617958365901</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.929553729950953</v>
+        <v>-5.916101441230843</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-6.349808340895855</v>
+        <v>-6.336252294544252</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-9.873671914279946</v>
+        <v>-9.884101549978098</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>167</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>8.564915410777083</v>
+        <v>8.57461580893402</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.764290741536726</v>
+        <v>5.775341382362456</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.980509862242691</v>
+        <v>2.992555941499582</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.317292186311221</v>
+        <v>1.329817225229448</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.975679216158433</v>
+        <v>1.987934686414143</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>7.659756553548682</v>
+        <v>7.670241583933326</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.183327098888057</v>
+        <v>5.194810677811873</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.310529991641957</v>
+        <v>8.321027351870057</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7.051925315040627</v>
+        <v>7.06512405399539</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.602997734803118</v>
+        <v>5.616402862455949</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>7.194651596114149</v>
+        <v>7.208108889824366</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.432627567830835</v>
+        <v>5.446079856550945</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.012372956886068</v>
+        <v>5.025929003237671</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1271272677238713</v>
+        <v>-0.1375569034220234</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>195</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.74338433048522</v>
+        <v>-2.729991622560973</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-7.422226689341016</v>
+        <v>-7.406682871372197</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-9.354717879076858</v>
+        <v>-9.338366007126822</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-12.81274532850477</v>
+        <v>-12.7952020890634</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-12.84358847131265</v>
+        <v>-12.82611745945508</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-12.55052298342869</v>
+        <v>-12.53310363730262</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-13.1520555101493</v>
+        <v>-13.13418255923909</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-16.18816492621452</v>
+        <v>-16.16920149403445</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-14.197882761115</v>
+        <v>-14.18468402216024</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-14.53518743332241</v>
+        <v>-14.52178230566958</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-14.22712024481937</v>
+        <v>-14.21366295110915</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-16.24401913875599</v>
+        <v>-16.23056685003588</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-15.12581221123946</v>
+        <v>-15.11225616488786</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-11.28634728921947</v>
+        <v>-11.29677692491762</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>216</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-8.056373597720977</v>
+        <v>-8.040583247348195</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.45210829546771</v>
+        <v>-6.436321916453281</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.767589277356869</v>
+        <v>-1.75345700045802</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7132740879175969</v>
+        <v>-0.699514030724302</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.490693603295512</v>
+        <v>-4.475579243202084</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.2359726642703066</v>
+        <v>-0.4779501314046257</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.713319257806155</v>
+        <v>-1.699035789487013</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.625486863536679</v>
+        <v>-5.872358097920639</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.612412675644805</v>
+        <v>-6.599213936690042</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.07364897178374</v>
+        <v>-6.060243844130909</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.037661555360671</v>
+        <v>-3.024204261650453</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.614389509126362</v>
+        <v>-1.600937220406252</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.2801706947435534</v>
+        <v>0.2937267410951563</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.321959824832007</v>
+        <v>-1.332389460530159</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>218</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-7.768811214138438</v>
+        <v>-7.752640820376158</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.518937323893304</v>
+        <v>-2.504400430752668</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.660411862324494</v>
+        <v>-2.901313796189875</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.740012691654954</v>
+        <v>-5.724184028186016</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.281254350985485</v>
+        <v>-6.265223354116529</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-7.818025447559855</v>
+        <v>-7.804982551265489</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.612771694452661</v>
+        <v>-5.596710319970249</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.410230322591964</v>
+        <v>-2.397049313296726</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.471230208774266</v>
+        <v>-2.458031469819502</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.027777412150812</v>
+        <v>-1.014372284497981</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7738151401381188</v>
+        <v>-0.7603578464279011</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.491725560774341</v>
+        <v>-3.478273272054231</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.618402190067762</v>
+        <v>-1.604846143716159</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.120974435773228</v>
+        <v>-4.13140407147138</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>211</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.752791452018364</v>
+        <v>1.765245853502392</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-6.020251191545029</v>
+        <v>-6.003742840470608</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-8.309725947856904</v>
+        <v>-8.296718816439302</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-8.658686307813717</v>
+        <v>-8.640792501629626</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-7.780854631753606</v>
+        <v>-7.763407877163715</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-10.3262061741661</v>
+        <v>-10.31316327787173</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-10.61951111790596</v>
+        <v>-10.87544515665616</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-13.45636276313285</v>
+        <v>-13.44318175383761</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.304092507134953</v>
+        <v>-8.29089376818019</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-7.732416744295797</v>
+        <v>-7.719011616642966</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.93717006861327</v>
+        <v>-7.923712774903052</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.059185015533245</v>
+        <v>-5.045732726813135</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.005505977189152</v>
+        <v>-4.991949930837549</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.28185099562365</v>
+        <v>-4.292280631321802</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>212</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.157105248485664</v>
+        <v>-4.398505761555775</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-5.983241310946454</v>
+        <v>-6.235744075551473</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.492890196218596</v>
+        <v>-4.479883064800994</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.837423044130475</v>
+        <v>-4.820573165404959</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.606161929782658</v>
+        <v>-1.591111912801999</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3653237656519011</v>
+        <v>-0.3522808693575357</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.4500574829240804</v>
+        <v>-0.4369912286236044</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.860637108120777</v>
+        <v>-1.847456098825539</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.336731333925833</v>
+        <v>-3.32353259497107</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.356667839708159</v>
+        <v>-1.343262712055328</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.504817390440934</v>
+        <v>-2.491360096730716</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.527038006680627</v>
+        <v>-1.513585717960517</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.834085070455608</v>
+        <v>-3.820529024104005</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.58436373817932</v>
+        <v>-3.594793373877472</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>218</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>5.759094380038043</v>
+        <v>5.771616669713666</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.776160200902154</v>
+        <v>2.789070010478206</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.09064792473851213</v>
+        <v>0.1036550561561143</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.2194470263392034</v>
+        <v>0.2343071962965482</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.531901933244718</v>
+        <v>-3.51523243186017</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.9408820138776264</v>
+        <v>-0.927839117583261</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.860478116471064</v>
+        <v>-2.847411862170588</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.034083533601134</v>
+        <v>-1.020902524305896</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.2810633692073878</v>
+        <v>0.294262108162151</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.48649300848119</v>
+        <v>-1.473087880828359</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7738151401382183</v>
+        <v>-0.7603578464280005</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.198147579122747</v>
+        <v>-1.184695290402637</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.6751757915834133</v>
+        <v>0.6887318379350162</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9099652614613021</v>
+        <v>-0.9203948971594542</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>197</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-5.047798198987593</v>
+        <v>-5.03527590931197</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.428288208982103</v>
+        <v>0.4411980185581541</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.03109206345607873</v>
+        <v>0.04409919487368086</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.694968188840008</v>
+        <v>2.708900986339316</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.100942123250661</v>
+        <v>-1.383343818577906</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.226956667256765</v>
+        <v>1.23999956355113</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.172679802776479</v>
+        <v>3.185746057076955</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1674253380050672</v>
+        <v>0.180606347300305</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.9088029745732271</v>
+        <v>-0.8956042356184639</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.266542372799073</v>
+        <v>-2.253137245146242</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.589618008467106</v>
+        <v>1.603075302177324</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.4064556869794487</v>
+        <v>-0.3930033982593386</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.334324511122098</v>
+        <v>-1.320768464770495</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9458536739459618</v>
+        <v>0.9354240382478096</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>184</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.422479605804732</v>
+        <v>-4.409957316129109</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.874926246090837</v>
+        <v>-3.862016436514786</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.6182636722801789</v>
+        <v>0.631270803697781</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.86950292761928</v>
+        <v>4.565122501626639</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.331081712547181</v>
+        <v>4.344192516922121</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.8241758241758816</v>
+        <v>0.837218720470247</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.000311672120873</v>
+        <v>4.013377926421349</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.902693490730734</v>
+        <v>1.915874500025971</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.298215343678997</v>
+        <v>1.31141408263376</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.165481462998763</v>
+        <v>3.178886590651594</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.504206399550753</v>
+        <v>3.517663693260971</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2777199916787936</v>
+        <v>0.2911722803989036</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.574856685081713</v>
+        <v>2.588412731433316</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.281099756488445</v>
+        <v>2.270670120790292</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>181</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.007250474906044246</v>
+        <v>0.005271814769578498</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5.011010166273287</v>
+        <v>5.023919975849338</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.301224332604868</v>
+        <v>1.31423146402247</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.3265050895218238</v>
+        <v>0.339484231920288</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2119161255504736</v>
+        <v>-0.1988053211755343</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.400442939237138</v>
+        <v>3.413485835531503</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.078140161191385</v>
+        <v>6.091206415491861</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.505984386719213</v>
+        <v>4.519165396014451</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.787525937000936</v>
+        <v>2.800724675955699</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.04237312766368</v>
+        <v>3.055778255316511</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.837619803346101</v>
+        <v>2.851077097056319</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.767030585000917</v>
+        <v>1.780482873721027</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.2418035983654718</v>
+        <v>0.2553596447170747</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.596497306332303</v>
+        <v>1.586067670634151</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>164</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.433390948082639</v>
+        <v>5.445913237758262</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.212061237557549</v>
+        <v>3.2249710471336</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.9879242382779623</v>
+        <v>1.000931369695564</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.150115312041372</v>
+        <v>-3.137136169642908</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6397560393086579</v>
+        <v>-0.6266452349337186</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.781338491836969</v>
+        <v>-2.768295595542604</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.866072209109248</v>
+        <v>-2.853005954808772</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.3252809774752379</v>
+        <v>0.3384619867704757</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.345475006268039</v>
+        <v>-0.3322762673132758</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.6336681013868883</v>
+        <v>0.6470732290397194</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7905974180526343</v>
+        <v>-0.7771401243424165</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.365970358268179</v>
+        <v>-1.352518069548069</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-3.005737164335109</v>
+        <v>-2.992181117983506</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.2927646557461259</v>
+        <v>0.2823350200479737</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>133</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.869378169834036</v>
+        <v>-2.856855880158413</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.7215532865577785</v>
+        <v>-0.7086434769817274</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.620181391650604</v>
+        <v>-2.607174260233002</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.489928259043019</v>
+        <v>-2.476949116644555</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-7.539627669603917</v>
+        <v>-7.526516865228977</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.738426333392098</v>
+        <v>-5.725383437097733</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.071280351416085</v>
+        <v>-5.058214097115609</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-7.042223148693999</v>
+        <v>-7.029042139398761</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.591944839387494</v>
+        <v>-2.578746100432731</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.821087870321506</v>
+        <v>1.834492997974337</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.143063950236758</v>
+        <v>-2.129606656526541</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.108680792891327</v>
+        <v>-2.095228504171217</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.025176005339901</v>
+        <v>-1.011619958988298</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.480184424680665</v>
+        <v>1.469754788982513</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>133</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.6137390720896718</v>
+        <v>-0.6012167824140491</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.293484307427271</v>
+        <v>5.306394117003322</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>8.658014097071415</v>
+        <v>8.671021228489018</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.780748432686302</v>
+        <v>5.793727575084766</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>8.249846014606611</v>
+        <v>8.26295681898155</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>11.55480674931484</v>
+        <v>11.5678496456092</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.214433934298121</v>
+        <v>9.227500188598597</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>12.50664903175721</v>
+        <v>12.51983004105245</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10.19001004783046</v>
+        <v>10.20320878678523</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.588005163554385</v>
+        <v>8.601410291207216</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.38325183923692</v>
+        <v>8.396709132947137</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.169514695830486</v>
+        <v>9.182966984550596</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>10.25301948338173</v>
+        <v>10.26657552973333</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.239582920921215</v>
+        <v>5.229153285223063</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>103</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>7.700736437071576</v>
+        <v>7.713258726747199</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>8.030910396922849</v>
+        <v>8.0438202064989</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.606915476733981</v>
+        <v>8.619922608151583</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>13.59153754138037</v>
+        <v>13.60451668377883</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>12.08224253990043</v>
+        <v>12.09535334427537</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.554441759169485</v>
+        <v>6.567484655463851</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8.41145561471275</v>
+        <v>8.424521869013226</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>7.94427221593125</v>
+        <v>7.957453225226487</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.883272329748948</v>
+        <v>7.896471068703711</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>11.88751607675991</v>
+        <v>11.90092120441274</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9.7410151796268</v>
+        <v>9.754472473337017</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>13.65889348260323</v>
+        <v>13.67234577132334</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.355143726027329</v>
+        <v>9.368699772378932</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>8.633991271895852</v>
+        <v>8.623561636197699</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>114</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1381406271584424</v>
+        <v>0.1506629168340652</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.666917891387222</v>
+        <v>4.679827700963273</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.394856202334445</v>
+        <v>3.407863333752047</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.738048559794848</v>
+        <v>-1.725069417396384</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.495460049694337</v>
+        <v>6.508570854069276</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.284130057585436</v>
+        <v>3.297172953879802</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.708168270137719</v>
+        <v>6.721234524438195</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.363791888900032</v>
+        <v>5.37697289819527</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.671213055349298</v>
+        <v>2.684411794304062</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.698280852777572</v>
+        <v>2.711685980430403</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.12510647582841</v>
+        <v>5.138563769538628</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.650717703349279</v>
+        <v>1.66416999206939</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.107656074860522</v>
+        <v>2.121212121212125</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.480184424680708</v>
+        <v>1.469754788982556</v>
       </c>
     </row>
     <row r="30">
@@ -1823,202 +1823,202 @@
         <v>107</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>12.92712242745357</v>
+        <v>12.93964471712919</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>9.446389935984598</v>
+        <v>9.459299745560649</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.24778291163102</v>
+        <v>6.260790043048623</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>11.05093324050015</v>
+        <v>11.06391238289861</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>10.51251202542805</v>
+        <v>10.52562282980299</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>11.74453340239606</v>
+        <v>11.75757629869042</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.856061367366742</v>
+        <v>8.869127621667218</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.32345740783763</v>
+        <v>9.336638417132868</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>11.13161640016003</v>
+        <v>11.1448151391148</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>10.28149121513205</v>
+        <v>10.29489634278488</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.01131733006672</v>
+        <v>11.02477462377693</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.04570048741229</v>
+        <v>11.0591527761324</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>9.690866437215</v>
+        <v>9.704422483566603</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>14.61348496575292</v>
+        <v>14.60305533005477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 81.1</t>
+          <t>X ≈ 81.09</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.669826985912472</v>
+        <v>6.281970567403796</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.099069699478832</v>
+        <v>6.732640144443053</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.642976503086352</v>
+        <v>2.214157419481865</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.308403017367375</v>
+        <v>-1.779328777135937</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-5.410401835386324</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.569790457989249</v>
+        <v>-3.051172135648152</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.427108477799756</v>
+        <v>2.018756680343451</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.041557732079482</v>
+        <v>5.67539937676289</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-3.182707460225295</v>
+        <v>-2.633005460172313</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.012424481987921</v>
+        <v>-3.482924256502137</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-5.257994132836053</v>
+        <v>-4.718553249813851</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-3.182794648960154</v>
+        <v>-2.622319427355492</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.562232933374418</v>
+        <v>-0.9806146105658371</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.332919764363375</v>
+        <v>-2.81673463044234</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 83.58</t>
+          <t>X ≈ 83.57</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>8.506561679790025</v>
+        <v>7.915123573426044</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.8949880668257819</v>
+        <v>0.3633434209562907</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.909166095607176</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.63037249283669</v>
+        <v>10.98988628870048</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>10.09195127776451</v>
+        <v>10.4515967356048</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.389393215480212</v>
+        <v>6.788574725635932</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.304659498207911</v>
+        <v>2.743468326765807</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.837476099426389</v>
+        <v>6.236795722583011</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.776476213244116</v>
+        <v>8.156011585862274</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.92635102821616</v>
+        <v>6.31599377963137</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.72159770389856</v>
+        <v>4.131094601569195</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.755980861244012</v>
+        <v>8.125868793528419</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>8.335726250299139</v>
+        <v>7.705717940215095</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.585447582575426</v>
+        <v>8.921552600342615</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 86.06</t>
+          <t>X ≈ 86.05</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>62</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-5.719244771822851</v>
+        <v>-5.706722482147228</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.572407421664479</v>
+        <v>5.585317231240531</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.01624839248724</v>
+        <v>10.02925552390484</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>13.37230797670762</v>
+        <v>13.38528711910609</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>7.995177084216124</v>
+        <v>8.008287888591063</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.292619021931756</v>
+        <v>8.305661918226122</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>13.04659498207881</v>
+        <v>13.05966123637928</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10.9665083574909</v>
+        <v>10.97968936678614</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>18.97002460034081</v>
+        <v>18.98322333929558</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>19.73280264111939</v>
+        <v>19.74620776877222</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>16.3022428651889</v>
+        <v>16.31570015889912</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>11.49791634511503</v>
+        <v>11.51136863383514</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>17.52927463739584</v>
+        <v>17.54283068374744</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>14.55318951805926</v>
+        <v>14.5427598823611</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>43</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>7.971677958859757</v>
+        <v>7.98420024853538</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>11.01126713659318</v>
+        <v>11.02417694616923</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>15.26756122069429</v>
+        <v>15.28056835211189</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>17.72339574865062</v>
+        <v>17.73637489104909</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>12.5338117428808</v>
+        <v>12.54692254725574</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>15.1568350759453</v>
+        <v>15.16987797223966</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.42093856797538</v>
+        <v>10.43400482227585</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.27933656454268</v>
+        <v>12.29251757383792</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.21833667836037</v>
+        <v>12.23153541731513</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>9.042630097983604</v>
+        <v>9.056035225636435</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.48903956436369</v>
+        <v>13.50249685807391</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.84900411705796</v>
+        <v>15.86245640577807</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.10316811076419</v>
+        <v>13.1167241571158</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.67847083838929</v>
+        <v>15.66804120269114</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2217,46 +2217,46 @@
         <v>4081</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.01359468473477676</v>
+        <v>-0.01389111602531301</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.0005599143330954348</v>
+        <v>0.0002506738608971659</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.03886866225921182</v>
+        <v>-0.03917067355361326</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.09089890080635854</v>
+        <v>-0.09118759722635872</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1024727867989554</v>
+        <v>-0.1027618787407505</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01268088671304923</v>
+        <v>0.01236518978871715</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.06365142382571065</v>
+        <v>0.06332262139290634</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.09934589874112021</v>
+        <v>0.09900553054692551</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1987528350311152</v>
+        <v>0.1983876296339986</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2926585698420183</v>
+        <v>0.2922653357955483</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2976447281454568</v>
+        <v>0.2972489251308446</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2968921792253951</v>
+        <v>0.2964965837138109</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2825530084466266</v>
+        <v>0.2821583378070116</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.2872363598358731</v>
+        <v>0.276806724137721</v>
       </c>
     </row>
     <row r="7">
@@ -2269,46 +2269,46 @@
         <v>4040</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1242379253432446</v>
+        <v>-0.124636731249872</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.118341975139181</v>
+        <v>-0.1187556280404323</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1542016274251381</v>
+        <v>-0.154609869745471</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1834086877017285</v>
+        <v>-0.1838088585920161</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1649657182829287</v>
+        <v>-0.1653750628346131</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.00225491894038754</v>
+        <v>-0.002702228146411301</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1242343869869345</v>
+        <v>0.1237549099089179</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1403191154956147</v>
+        <v>0.1398316020483676</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1919064803064003</v>
+        <v>0.1914054837192509</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.3201180329156372</v>
+        <v>0.3195781143259708</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.376718931013869</v>
+        <v>0.3761630856622276</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.4003758129886279</v>
+        <v>0.3998141494693144</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.439686646338707</v>
+        <v>0.4391115468363083</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4666357013872755</v>
+        <v>0.4562060656891234</v>
       </c>
     </row>
     <row r="8">
@@ -2321,46 +2321,46 @@
         <v>3987</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.230372553768369</v>
+        <v>-0.2309160305343525</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1530359451802354</v>
+        <v>-0.1536175024428914</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2341813653149885</v>
+        <v>-0.2347474453217089</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3155734531092662</v>
+        <v>-0.3161179669665088</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.2397133029613983</v>
+        <v>-0.240283263205896</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1038466443095132</v>
+        <v>-0.1044474927310972</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.0003770038427433064</v>
+        <v>-0.0002512129398013485</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02725335949145347</v>
+        <v>-0.02788033179928817</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.07589991657658146</v>
+        <v>0.07524609448342545</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2421405019003657</v>
+        <v>0.2414349331178016</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.3272632842445375</v>
+        <v>0.3265336943506583</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3256899886261664</v>
+        <v>0.3249608511423645</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3460096714177467</v>
+        <v>0.3452702605423852</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3699973693825243</v>
+        <v>0.3595677336843721</v>
       </c>
     </row>
     <row r="9">
@@ -2373,46 +2373,46 @@
         <v>3937</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2512290473445091</v>
+        <v>-0.2519393334725493</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2783520244058622</v>
+        <v>-0.2790795748269659</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3807424902144234</v>
+        <v>-0.3814502949725735</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3888972840395937</v>
+        <v>-0.3896014699613062</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.3556774313402258</v>
+        <v>-0.35639836410801</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1458680732057758</v>
+        <v>-0.1466381971273165</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.01158667405157843</v>
+        <v>0.01077496610552231</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.0102396366142159</v>
+        <v>-0.01105311710938395</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.04431068899936008</v>
+        <v>0.04348205879783507</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2747512313649665</v>
+        <v>0.2738511038253293</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.3129108865249464</v>
+        <v>0.3119976080709677</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3472940438703773</v>
+        <v>0.3607463325904874</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.3080401949270026</v>
+        <v>0.3215962412786055</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.3545611208024795</v>
+        <v>0.3441314851043273</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3864</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4149461952422513</v>
+        <v>-0.4158669856195374</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.3860036687114246</v>
+        <v>-0.3869639877861459</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.586163254082372</v>
+        <v>-0.5870801199234705</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5453381014785705</v>
+        <v>-0.5462634513058049</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4495323097257966</v>
+        <v>-0.4504934734161097</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2672768982737139</v>
+        <v>-0.2682798354986673</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.053499281207678</v>
+        <v>-0.05455966631273412</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.06681774433977239</v>
+        <v>-0.06788439632103405</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.04167673070850952</v>
+        <v>0.04058028070377162</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2151709039925578</v>
+        <v>0.2140123007590233</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3468565030704198</v>
+        <v>0.3603137967806376</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3812396604158508</v>
+        <v>0.3946919491359608</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.32330389005066</v>
+        <v>0.3368599364022629</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.3659858848528259</v>
+        <v>0.3555562491546738</v>
       </c>
     </row>
     <row r="11">
@@ -2477,98 +2477,98 @@
         <v>3728</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.04495022815752492</v>
+        <v>-0.04645910169540457</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2773888068359014</v>
+        <v>-0.2788829638443673</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.5507507870265087</v>
+        <v>-0.5521840008585741</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5667351665098721</v>
+        <v>-0.5681610823016783</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.528193378008325</v>
+        <v>-0.5296460057020127</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2429754876280796</v>
+        <v>-0.2444966500792063</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.0183102150057195</v>
+        <v>-0.01989482626976979</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1994063943325628</v>
+        <v>0.1977490411794065</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2068865109110192</v>
+        <v>0.2052245500540835</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5250634745680856</v>
+        <v>0.5232906155096444</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.5080783905938659</v>
+        <v>0.5215356843040837</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5692855822740555</v>
+        <v>0.5827378709941655</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6050395550201344</v>
+        <v>0.6185956013717373</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5596965096140281</v>
+        <v>0.5492668739158759</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 32.76</t>
+          <t>X &gt; 32.77</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3600</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.08213011621884192</v>
+        <v>-0.08413021728969028</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1820842924755937</v>
+        <v>-0.1841198619573845</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4233415382733199</v>
+        <v>-0.4253265163931488</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5000019870523715</v>
+        <v>-0.5019617313760634</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4962840163531439</v>
+        <v>-0.4982666279853802</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.07272168876629337</v>
+        <v>-0.07481139100016065</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.05202207455435826</v>
+        <v>0.04989339058774078</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2665235862356141</v>
+        <v>0.2643161870114596</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3875873243552022</v>
+        <v>0.3853428222349535</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.6485732504383819</v>
+        <v>0.661978378091213</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6938199261208027</v>
+        <v>0.7072772198310204</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5337586390217979</v>
+        <v>0.5472109277419079</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.7523929169657819</v>
+        <v>0.7659489633173848</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.7243364714642837</v>
+        <v>0.7139068357661316</v>
       </c>
     </row>
     <row r="13">
@@ -2578,49 +2578,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3477</v>
+        <v>3475</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.04006672767052066</v>
+        <v>-0.0124889352415849</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.0005343212339354864</v>
+        <v>-0.0008015206696754262</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2076038668738889</v>
+        <v>-0.207723594510604</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4351071165831897</v>
+        <v>-0.4353613782667267</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7856700954041216</v>
+        <v>-0.7857425155617008</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3002619569336247</v>
+        <v>-0.3003520457419953</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.08194584815600336</v>
+        <v>-0.0819292216146934</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1853771920083318</v>
+        <v>0.1857160675942211</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3416185773510776</v>
+        <v>0.3420339855705379</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6419104184951436</v>
+        <v>0.6591806163006453</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6960009250662509</v>
+        <v>0.7422492422131199</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.4715402515229954</v>
+        <v>0.488857610395776</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5977337280097856</v>
+        <v>0.6154693470104178</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.5023299524344793</v>
+        <v>0.4958812562297652</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>3299</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.04739652552505191</v>
+        <v>0.04403105141302888</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.08560833914044252</v>
+        <v>0.08212655153793236</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.04007093407905415</v>
+        <v>0.03657581086009287</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.2975718002302372</v>
+        <v>-0.3009582921256282</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8196174684499056</v>
+        <v>-0.8228822109274674</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1422638581338802</v>
+        <v>-0.1457165229922666</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.03193222548061669</v>
+        <v>0.02841948168133968</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.03602111306688727</v>
+        <v>0.03247529053980003</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.1872067376454183</v>
+        <v>0.2004054766001815</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5495701855365667</v>
+        <v>0.5629753131893978</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7691878827406597</v>
+        <v>0.7826451764508775</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.5610733135022699</v>
+        <v>0.5745256022223799</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8076874506628542</v>
+        <v>0.8212434970144571</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.5421011139485472</v>
+        <v>0.5316714782503951</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>3140</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2869874821414768</v>
+        <v>0.2827434357934777</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3450834260120388</v>
+        <v>0.3406910127221181</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.22189996436272</v>
+        <v>0.2175130142151147</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.05149208571199893</v>
+        <v>0.04716721552130565</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5014308412300892</v>
+        <v>-0.5056249407613151</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.09976877245024696</v>
+        <v>0.09540461320628424</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5100081132986247</v>
+        <v>0.5055042375497365</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.3470302395537814</v>
+        <v>0.342538675101757</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.508960289677205</v>
+        <v>0.5221590286319682</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8371790536938732</v>
+        <v>0.8505841813467043</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.046438468229788</v>
+        <v>1.059895761940005</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.8897388230274501</v>
+        <v>0.9031911117475602</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.170121154757709</v>
+        <v>1.183677201109312</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.069524015696423</v>
+        <v>1.059094379998271</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2973</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.178002078599242</v>
+        <v>-0.18302941530456</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.04067453879622462</v>
+        <v>0.03541465492530449</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.06694273161937048</v>
+        <v>0.06163270178440428</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.01961071173167994</v>
+        <v>-0.02488207866680625</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6405756039559165</v>
+        <v>-0.6456937122844693</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3248924988055464</v>
+        <v>-0.3300907699458904</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2474974269234309</v>
+        <v>0.2420955004075296</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.1002971935436747</v>
+        <v>-0.1056307191196666</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.141427440960193</v>
+        <v>0.1546261799149562</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5694724543850143</v>
+        <v>0.5828775820378453</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.7010797086076295</v>
+        <v>0.7145370023178472</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6345546923910064</v>
+        <v>0.6480069811111164</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9542933542345224</v>
+        <v>0.9678494005861253</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.136742570802774</v>
+        <v>1.126312935104622</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>2778</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.002073349448913575</v>
+        <v>-0.004246970950717355</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5645282967108258</v>
+        <v>0.5578081097949905</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.72829039867689</v>
+        <v>0.7214598249801156</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8783954978690289</v>
+        <v>0.8715226736828541</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2160073726943921</v>
+        <v>0.2093036349791291</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.5332781075664954</v>
+        <v>0.5264922067044182</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.188070797236321</v>
+        <v>1.181035105026353</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.028980779052013</v>
+        <v>1.021941743482337</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.147966494021624</v>
+        <v>1.161165232976387</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.629734757517824</v>
+        <v>1.643139885170655</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.748955515273671</v>
+        <v>1.762412808983889</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.819335792849486</v>
+        <v>1.832788081569596</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.083026466281837</v>
+        <v>2.096582512633439</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.00877371648469</v>
+        <v>1.998344080786538</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>2562</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.681474028835602</v>
+        <v>0.6732895769422811</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.156094847807843</v>
+        <v>1.147477151820603</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.9387158514572462</v>
+        <v>0.9301179179912893</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.012587781448225</v>
+        <v>1.003975416911551</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.6128252535741012</v>
+        <v>0.6042820509382025</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5981329735761491</v>
+        <v>0.6111758698705145</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.432684478691883</v>
+        <v>1.423851386530998</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.590013179832319</v>
+        <v>1.603194189127557</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.802237337365867</v>
+        <v>1.81543607632063</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.27920036467205</v>
+        <v>2.292605492324881</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.152511052844716</v>
+        <v>2.165968346554934</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.108830197699902</v>
+        <v>2.122282486420012</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.235023674186699</v>
+        <v>2.248579720538302</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.289584975237382</v>
+        <v>2.27915533953923</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>2344</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.467379396996158</v>
+        <v>1.45692986133453</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.49788538254797</v>
+        <v>1.487114230745938</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.273447012551294</v>
+        <v>1.286454143968896</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.640602671864805</v>
+        <v>1.629717208307149</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.253998186080075</v>
+        <v>1.243169499019238</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.380864430831977</v>
+        <v>1.393907327126342</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.087935948719831</v>
+        <v>2.076787586197064</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.962049478265982</v>
+        <v>1.97523048756122</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.199684404370373</v>
+        <v>2.212883143325136</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.586760584530154</v>
+        <v>2.600165712182985</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.424669376253526</v>
+        <v>2.438126669963744</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.629700997762782</v>
+        <v>2.643153286482892</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.593405431186476</v>
+        <v>2.606961477538078</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.885788879503728</v>
+        <v>2.875359243805576</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>2133</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.439145949452943</v>
+        <v>1.426430717242908</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.24159228228244</v>
+        <v>2.228122595502938</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.221430835639019</v>
+        <v>2.234437967056621</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.659425913642671</v>
+        <v>2.645693555609853</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.147741244946879</v>
+        <v>2.134115502945441</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.538947833389216</v>
+        <v>2.551990729683581</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.344978298020365</v>
+        <v>3.358044552320841</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.487265128962257</v>
+        <v>3.500446138257495</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.238735941326595</v>
+        <v>3.251934680281359</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.607551215745467</v>
+        <v>3.620956343398298</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.449680216791222</v>
+        <v>3.46313751050144</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.390298723409977</v>
+        <v>3.403751012130087</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.34510271537178</v>
+        <v>3.358658761723383</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.594824047648068</v>
+        <v>3.584394411949916</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>1921</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.056743687070316</v>
+        <v>2.069265976745939</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.149278238432636</v>
+        <v>3.162188048008687</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.962417852168855</v>
+        <v>2.975424983586457</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.486772076603579</v>
+        <v>3.469664687757245</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.562018950851439</v>
+        <v>2.54522857537566</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.859460888567099</v>
+        <v>2.872503784861465</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.763795364943967</v>
+        <v>3.776861619244443</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.077455276938103</v>
+        <v>4.090636286233341</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.964399170037424</v>
+        <v>3.977597908992188</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.155398399377006</v>
+        <v>4.168803527029837</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.106813737214559</v>
+        <v>4.120271030924776</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.932972011686495</v>
+        <v>3.946424300406605</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.137392049362099</v>
+        <v>4.150948095713701</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.387113381638386</v>
+        <v>4.376683745940234</v>
       </c>
     </row>
     <row r="22">
@@ -3049,46 +3049,46 @@
         <v>1703</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.582808014100877</v>
+        <v>1.5953303037765</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.197040852749517</v>
+        <v>3.209950662325568</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.330031383689587</v>
+        <v>3.343038515107189</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.905020380160614</v>
+        <v>3.883820843446287</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.342098077529634</v>
+        <v>3.321024523454</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.34594048500454</v>
+        <v>3.358983381298906</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.611764606839721</v>
+        <v>4.624830861140197</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.731780268539723</v>
+        <v>4.74496127783496</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.435900758164813</v>
+        <v>4.449099497119576</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.877613506196198</v>
+        <v>4.891018633849029</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.731580087926766</v>
+        <v>4.745037381636983</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.589803527127742</v>
+        <v>4.603255815847852</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.580588258519903</v>
+        <v>4.594144304871506</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5.065189214988784</v>
+        <v>5.054759579290632</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>1506</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.450158229225991</v>
+        <v>2.462680518901614</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.559221643468099</v>
+        <v>3.57213145304415</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.761565942843639</v>
+        <v>3.774573074261241</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.063307419795514</v>
+        <v>4.03751221917674</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.923292579225333</v>
+        <v>3.936403383600272</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.623124955188011</v>
+        <v>3.636167851482377</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.800011423838704</v>
+        <v>4.81307767813918</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.328843961312181</v>
+        <v>5.342024970607419</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.135041950295886</v>
+        <v>5.148240689250649</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.812141200858925</v>
+        <v>5.825546328511756</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.142580439622357</v>
+        <v>5.156037733332575</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.243364659384781</v>
+        <v>5.256816948104891</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.354318547775868</v>
+        <v>5.367874594127471</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5.604039880052156</v>
+        <v>5.593610244354004</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>1322</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.406712965720438</v>
+        <v>3.41923525539606</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.593929065312906</v>
+        <v>4.606838874888957</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.199060358716316</v>
+        <v>4.212067490133919</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.951098665302645</v>
+        <v>3.964077807701109</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.866535241455878</v>
+        <v>3.879646045830818</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4.012691248763069</v>
+        <v>4.025734145057434</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.91131607914587</v>
+        <v>4.924382333446346</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.805706054040606</v>
+        <v>5.818887063335843</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.669063202654065</v>
+        <v>5.682261941608829</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.180511391302389</v>
+        <v>6.19391651895522</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.37061434535093</v>
+        <v>5.384071639061148</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.934498259126009</v>
+        <v>5.947950547846119</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.741172543793816</v>
+        <v>5.754728590145419</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.066536841274342</v>
+        <v>6.05610720557619</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>1141</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.948279471201062</v>
+        <v>3.960801760876684</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.527766331505873</v>
+        <v>4.540676141081924</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.658752138493853</v>
+        <v>4.671759269911455</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.526078014309071</v>
+        <v>4.539057156707536</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.513511312821471</v>
+        <v>4.52662211719641</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.10981389909103</v>
+        <v>4.122856795385395</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.726219533264853</v>
+        <v>4.739285787565329</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>6.011884513098607</v>
+        <v>6.025065522393845</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6.126169464777831</v>
+        <v>6.139368203732595</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>6.678322982642108</v>
+        <v>6.691728110294939</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.772430306878427</v>
+        <v>5.785887600588644</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.595595234600715</v>
+        <v>6.609047523320825</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6.61355271830962</v>
+        <v>6.627108764661223</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.775631631655152</v>
+        <v>6.765201995957</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>977</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.698987473034649</v>
+        <v>3.711509762710271</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.748621638985433</v>
+        <v>4.761531448561485</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.274940240474827</v>
+        <v>5.287947371892429</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.814609954453871</v>
+        <v>5.827589096852336</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.378542884724588</v>
+        <v>5.391653689099527</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.266568241068704</v>
+        <v>5.279611137363069</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.000667686539522</v>
+        <v>6.013733940839998</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.966442322558422</v>
+        <v>6.979623331853659</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>7.212504872404779</v>
+        <v>7.225703611359542</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>7.692983576834379</v>
+        <v>7.70638870448721</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.874105380459483</v>
+        <v>6.8875626741697</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.932029991233776</v>
+        <v>7.945482279953886</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>8.228254397689078</v>
+        <v>8.241810444040681</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.863850857908048</v>
+        <v>7.853421222209896</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>844</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.734049831448793</v>
+        <v>4.746572121124416</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.610627877252305</v>
+        <v>5.623537686828357</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.51907670620075</v>
+        <v>6.532083837618352</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7.123263488097344</v>
+        <v>7.136242630495808</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.4142261592811</v>
+        <v>7.427336963656039</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.000767623063112</v>
+        <v>7.013810519357477</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.745417792046752</v>
+        <v>7.758484046347228</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.173968990421649</v>
+        <v>9.187149999716887</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.757518867272516</v>
+        <v>8.770717606227279</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.618294156178237</v>
+        <v>8.631699283831068</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.295057419538395</v>
+        <v>8.308514713248613</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.514274700106569</v>
+        <v>9.527726988826679</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.686437150773038</v>
+        <v>9.699993197124641</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.86980777214886</v>
+        <v>8.859378136450708</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>711</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.734409781055845</v>
+        <v>5.746932070731468</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.669952905081743</v>
+        <v>5.682862714657794</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.118966055025233</v>
+        <v>6.131973186442835</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.374394996352848</v>
+        <v>7.387374138751312</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7.257914709550725</v>
+        <v>7.271025513925665</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.148886886366249</v>
+        <v>6.161929782660614</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.470622929994107</v>
+        <v>7.483689184294583</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.550556268202762</v>
+        <v>8.563737277497999</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>8.48955638202046</v>
+        <v>8.502755120975223</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.623960029622637</v>
+        <v>8.637365157275468</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>8.278559729215033</v>
+        <v>8.292017022925251</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>9.57876567137059</v>
+        <v>9.5922179600907</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.580451988695735</v>
+        <v>9.594008035047338</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.548879368792001</v>
+        <v>9.538449733093849</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>608</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.401298521895292</v>
+        <v>5.413820811570915</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.269988066825768</v>
+        <v>5.282897876401819</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.697487781281808</v>
+        <v>5.71049491269941</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.32116196652089</v>
+        <v>6.334141108919354</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.440635488290823</v>
+        <v>6.453746292665762</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.080182689164381</v>
+        <v>6.093225585458747</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.311238445576308</v>
+        <v>7.324304699876784</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.653265573110602</v>
+        <v>8.66644658240584</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.5922656869283</v>
+        <v>8.605464425883063</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.071087870321421</v>
+        <v>8.084492997974252</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.030808230214362</v>
+        <v>8.044265523924579</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.887559808612437</v>
+        <v>8.901012097332547</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.618620987141206</v>
+        <v>9.632177033492809</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>9.703868635206973</v>
+        <v>9.693438999508821</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>494</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.615873420680714</v>
+        <v>6.628395710356337</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.40915810731159</v>
+        <v>5.422067916887642</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.22886429950043</v>
+        <v>6.241871430918032</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.180979780286066</v>
+        <v>8.19395892268453</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.427983666428474</v>
+        <v>6.441094470803414</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.725425604144135</v>
+        <v>6.738468500438501</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.450408486062145</v>
+        <v>7.463474740362621</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.412374884851495</v>
+        <v>9.425555894146733</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.958662448061908</v>
+        <v>9.971861187016671</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.310966412831547</v>
+        <v>9.324371540484378</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.70135478891882</v>
+        <v>8.714812082629038</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.55760029444239</v>
+        <v>10.5710525831625</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.35192058228291</v>
+        <v>11.36547662863451</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>11.6016419145592</v>
+        <v>11.59121227886104</v>
       </c>
     </row>
     <row r="31">
@@ -3517,150 +3517,150 @@
         <v>387</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.870902765061345</v>
+        <v>4.883425054736968</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.292920883363237</v>
+        <v>4.305830692939288</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.223633572115489</v>
+        <v>6.236640703533091</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.387478435989138</v>
+        <v>7.400457578387602</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.298669624017741</v>
+        <v>5.31178042839268</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.337713628916866</v>
+        <v>5.350756525211231</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.06176544136035</v>
+        <v>7.074831695660826</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.436959303560762</v>
+        <v>9.450140312856</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.634357350194996</v>
+        <v>9.647556089149759</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.042630097983604</v>
+        <v>9.056035225636435</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.062682975216418</v>
+        <v>8.076140268926636</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11.81117844668153</v>
+        <v>11.82473449303313</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.76891011487514</v>
+        <v>10.75848047917699</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 82.34</t>
+          <t>X &gt; 82.33</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.599987285326357</v>
+        <v>4.415635693603583</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.680455194853444</v>
+        <v>3.494104772953548</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.437835623204961</v>
+        <v>7.582092008888161</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.33625484577785</v>
+        <v>10.47093784213168</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.759771346968662</v>
+        <v>8.898165530415312</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.019151000947303</v>
+        <v>8.161056801429709</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.972479567412044</v>
+        <v>8.766001614577334</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>10.92744149735027</v>
+        <v>10.71272607423887</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>13.98062846237904</v>
+        <v>13.75519219357817</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>13.13050327735111</v>
+        <v>13.2501009834552</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>12.57972919178785</v>
+        <v>12.35574465278121</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>15.03625767785302</v>
+        <v>14.80391590858481</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>16.34610687313648</v>
+        <v>16.10790298630589</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>15.21174516043007</v>
+        <v>15.29915587791172</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 84.82</t>
+          <t>X &gt; 84.81</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>189</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.53301670624505</v>
+        <v>2.545538995920673</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.15424732608502</v>
+        <v>5.167157135661071</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.46308232319214</v>
+        <v>8.476089454609742</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.18063704310122</v>
+        <v>10.19361618549969</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.05491424072747</v>
+        <v>8.068025045102409</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.881456707543656</v>
+        <v>8.894499603838021</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>13.09144435339464</v>
+        <v>13.10462536268988</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>16.73414817091604</v>
+        <v>16.7473469098708</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>16.94222404408917</v>
+        <v>16.955629171742</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>16.73747071977159</v>
+        <v>16.75092801348181</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>18.35915546441862</v>
+        <v>18.37260775313873</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>20.58440349897635</v>
+        <v>20.59795954532795</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>18.71772271485052</v>
+        <v>18.70729307915237</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>127</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.56167979002624</v>
+        <v>6.574202079701863</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.950106177061983</v>
+        <v>4.963015986638034</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.704843769678</v>
+        <v>7.717850901095602</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.622498477088648</v>
+        <v>8.635477619487112</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.084077262016478</v>
+        <v>8.097188066391418</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>9.168920774535287</v>
+        <v>9.181963670829653</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.44639178167247</v>
+        <v>11.45945803597294</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>14.12881468210356</v>
+        <v>14.1419956913988</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>15.64261794552755</v>
+        <v>15.65581668448232</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15.57989433530277</v>
+        <v>15.5932994629556</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.9499441605915</v>
+        <v>16.96340145430172</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.70873676675582</v>
+        <v>21.72218905547593</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>22.07588373061407</v>
+        <v>22.08943977696568</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>20.75080191328405</v>
+        <v>20.7403722775859</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>5.83989501312336</v>
+        <v>5.852417302798983</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.847369019206724</v>
+        <v>1.860278828782775</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.833452693562514</v>
+        <v>3.846459824980116</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.806236992050216</v>
+        <v>5.819347796425156</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>6.103678929765877</v>
+        <v>6.116721826060243</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>15.07557133752162</v>
+        <v>15.08875234681685</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>17.39552383229171</v>
+        <v>17.40872257124647</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>18.92635102821616</v>
+        <v>18.93975615586899</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>18.72159770389858</v>
+        <v>18.7350549976088</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>24.70836181362496</v>
+        <v>24.72181410234507</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>26.66905958363245</v>
+        <v>26.68261562998406</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>23.34735234448017</v>
+        <v>23.33692270878202</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that RSI-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that RSI-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3908,49 +3908,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.418797590635293</v>
+        <v>5.431707400211344</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.023928884038703</v>
+        <v>5.036936015456305</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.725610588074773</v>
+        <v>8.738589730473237</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.3776655634788</v>
+        <v>9.390776367853739</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.913202739289694</v>
+        <v>4.92624563558406</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.637992831541226</v>
+        <v>3.651059085841702</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.7898570518073456</v>
+        <v>0.8030380611025834</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.842571405803525</v>
+        <v>-2.829372666848762</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-7.264125162260029</v>
+        <v>-7.250720034607198</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.468878486577609</v>
+        <v>-7.455421192867391</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-7.434495329232178</v>
+        <v>-7.421043040512068</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.664273749700889</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.22178133308725</v>
+        <v>-7.615458243598944</v>
       </c>
     </row>
     <row r="7">
@@ -3960,49 +3960,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.306561679790022</v>
+        <v>4.319083969465645</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.494988066825769</v>
+        <v>7.50789787640182</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.100119360229179</v>
+        <v>7.113126491646781</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.83037249283668</v>
+        <v>8.843351635235145</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.291951277764511</v>
+        <v>8.30506208213945</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.789393215480167</v>
+        <v>3.802436111774533</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5046594982078929</v>
+        <v>0.5177257525083689</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.7625239005736049</v>
+        <v>-0.7493428912783671</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.623523786755911</v>
+        <v>-1.610325047801147</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.673648971783841</v>
+        <v>-5.66024384413101</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-7.478402296101422</v>
+        <v>-7.464945002391204</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-8.244019138755988</v>
+        <v>-8.230566850035878</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-9.464273749700894</v>
+        <v>-9.450717703349291</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-11.25326209484396</v>
+        <v>-10.82498205312275</v>
       </c>
     </row>
     <row r="8">
@@ -4012,49 +4012,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.371730219115861</v>
+        <v>5.384252508791484</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.007347617387566</v>
+        <v>6.020257426963617</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.736074416408961</v>
+        <v>6.749081547826563</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.113518560252409</v>
+        <v>9.126497702650873</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.451501839562255</v>
+        <v>7.464612643937194</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.939955013232982</v>
+        <v>4.952997909527348</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.169828037533726</v>
+        <v>3.182894291834202</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.264442391561218</v>
+        <v>3.277623400856456</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.518049246951961</v>
+        <v>1.531247985906724</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.141064702120921</v>
+        <v>-2.12765957446809</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.031211284865456</v>
+        <v>-4.017753991155239</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-3.996828127520025</v>
+        <v>-3.983375838799915</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.417082738464927</v>
+        <v>-4.403526692113324</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.567094790305958</v>
+        <v>-5.301386547504777</v>
       </c>
     </row>
     <row r="9">
@@ -4064,49 +4064,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.463083418920462</v>
+        <v>4.475605708596085</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6.764553284217079</v>
+        <v>6.777463093793131</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.674032403707436</v>
+        <v>7.687039535125038</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.239068145010599</v>
+        <v>8.252047287409063</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.700646929938429</v>
+        <v>7.713757734313369</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.519827998088864</v>
+        <v>4.53287089438323</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.261181237338327</v>
+        <v>2.274247491638803</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.228780447252475</v>
+        <v>2.241961456547713</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.732997952374525</v>
+        <v>1.746196691329288</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.160605493522972</v>
+        <v>-2.147200365870141</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.8001414265362</v>
+        <v>-2.786684132825982</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.405591191157733</v>
+        <v>-3.621871197861971</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.716905328648259</v>
+        <v>-2.938927310336183</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.991644928437822</v>
+        <v>-3.793403105754336</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.401298521895292</v>
+        <v>5.413820811570915</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.421303856299453</v>
+        <v>6.434213665875504</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8.329066728650226</v>
+        <v>8.342073860067828</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.130372492836678</v>
+        <v>8.143351635235142</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.934056540922406</v>
+        <v>6.947167345297345</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.928866899690703</v>
+        <v>4.941909795985069</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.54150160347104</v>
+        <v>2.554567857771517</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.403265573110602</v>
+        <v>2.41644658240584</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.355423581665136</v>
+        <v>1.368622320619899</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.81049107704699</v>
+        <v>-0.7970859493941589</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.483022758147627</v>
+        <v>-2.646523949759619</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.932760860610301</v>
+        <v>-3.095253318682744</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.179223915813843</v>
+        <v>-2.346081941759884</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.081219084091266</v>
+        <v>-2.936609960099503</v>
       </c>
     </row>
     <row r="11">
@@ -4168,101 +4168,101 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.461107134335478</v>
+        <v>0.4736294240111008</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.394988066825761</v>
+        <v>3.407897876401812</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5.272846632956458</v>
+        <v>5.28585376437406</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.630372492836678</v>
+        <v>5.643351635235142</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.319224005037235</v>
+        <v>5.332334809412174</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.116665942752896</v>
+        <v>3.129708839047261</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.44102313457153</v>
+        <v>1.454089388872006</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6038883458238331</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4507965140286387</v>
+        <v>-0.4375977750738755</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.119103517238386</v>
+        <v>-3.105698389585555</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.975441020474996</v>
+        <v>-3.083126820573014</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.504293111358727</v>
+        <v>-3.610976872814916</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.803861850387392</v>
+        <v>-3.910991675952026</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.662258839442956</v>
+        <v>-3.564570153809257</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 32.76</t>
+          <t>X &lt; 32.77</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.5821328572944111</v>
+        <v>0.5946551469700339</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.958256959620137</v>
+        <v>1.971166769196188</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.145110572882949</v>
+        <v>3.158117704300551</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.802604478776928</v>
+        <v>3.815583621175392</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.791424036991216</v>
+        <v>3.804534841366156</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.276915183845716</v>
+        <v>1.289958080140082</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.6649406932869795</v>
+        <v>0.6780069475874555</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.8567242520674654</v>
+        <v>-0.8435432427722276</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.444964911536225</v>
+        <v>-1.431766172581462</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.080691225304967</v>
+        <v>-3.160419591055444</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.368349386048514</v>
+        <v>-3.448043593940497</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.357093343702978</v>
+        <v>-2.438679724815415</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.743919767400008</v>
+        <v>-3.823862579674376</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.754977949339498</v>
+        <v>-3.681619221264349</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2522264196744146</v>
+        <v>0.1127439118287583</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6637741939934045</v>
+        <v>0.6629411040675208</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.424974851558659</v>
+        <v>1.420907471473875</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.71129734832801</v>
+        <v>2.703870367223615</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.485014861579536</v>
+        <v>4.471056318450685</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.181300729931039</v>
+        <v>2.174770405722654</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.229514989537371</v>
+        <v>1.225506732335461</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2492291028857494</v>
+        <v>-0.2502074445924976</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.8882636711489837</v>
+        <v>-0.8875584771959666</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.38334506440323</v>
+        <v>-2.457938368626692</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.65521389030431</v>
+        <v>-2.873891611337811</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.52703800668052</v>
+        <v>-1.606289393388479</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.158459796212519</v>
+        <v>-2.236824794521496</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.82939957899665</v>
+        <v>-1.787300893702458</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1398217874889625</v>
+        <v>-0.1272994978133397</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2003841632666408</v>
+        <v>0.2132939728426919</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1499471443853224</v>
+        <v>0.1629542758029245</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.543116465282147</v>
+        <v>1.556095607680611</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.530527626788619</v>
+        <v>3.543638431163558</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.072516062782114</v>
+        <v>1.085558959076479</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.5285400952228159</v>
+        <v>0.5416063495232919</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4057883841565797</v>
+        <v>0.4189693934518175</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.05110999365246727</v>
+        <v>-0.101255013357985</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.413119627710188</v>
+        <v>-1.462542694705718</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.246144231585291</v>
+        <v>-2.294864450032165</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.457398608190822</v>
+        <v>-1.507064545888412</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.391756428684722</v>
+        <v>-2.440798441526908</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.501257619736741</v>
+        <v>-1.459624085455317</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.8429528833167765</v>
+        <v>-0.8304305936411538</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.6098663021062691</v>
+        <v>-0.596956492530218</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4222107368582044</v>
+        <v>-0.4092036054406023</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1934792889531778</v>
+        <v>0.206458431351642</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.888067782618876</v>
+        <v>1.901178586993815</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.1466747688782348</v>
+        <v>0.1597176651726002</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.006020113442595</v>
+        <v>-0.9929538591421192</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5994171044571104</v>
+        <v>-0.5862360951618726</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.996118538942504</v>
+        <v>-1.035567766247752</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.988045858943373</v>
+        <v>-2.027202055987175</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.626990416841437</v>
+        <v>-2.665723212507935</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.150451887293997</v>
+        <v>-2.189671036988173</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.005737164335031</v>
+        <v>-3.044479886585151</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.801271167424602</v>
+        <v>-2.766445467756895</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4723093823798266</v>
+        <v>0.4848316720554493</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2809529791064733</v>
+        <v>0.2938627886825245</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.05316865012057548</v>
+        <v>0.0661757815381776</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3505061603387674</v>
+        <v>0.3634853027372316</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.900639665400263</v>
+        <v>1.913750469775202</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.195575337451764</v>
+        <v>1.20861823374613</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1422912119007123</v>
+        <v>-0.1292249576002362</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6436582213979847</v>
+        <v>0.6568392306932225</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1276467818059572</v>
+        <v>0.09460394133836303</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.9272054571394932</v>
+        <v>-0.9599093959704703</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.253276667960719</v>
+        <v>-1.285865504483255</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.088947889803762</v>
+        <v>-1.121689128092825</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.882394555070022</v>
+        <v>-1.914757938051714</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.426307245300343</v>
+        <v>-2.398136415538858</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.02092949588197968</v>
+        <v>0.03345178555760242</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.8004142320248064</v>
+        <v>-0.7875044224487553</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.267122019081164</v>
+        <v>-1.254114887663562</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.496064288772516</v>
+        <v>-1.483085146374052</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1666694118906662</v>
+        <v>-0.1535586075157269</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7312964396922368</v>
+        <v>-0.7182535433978714</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.965455444320853</v>
+        <v>-1.952389190020376</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.71424803850465</v>
+        <v>-1.701067029209412</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.880605023276402</v>
+        <v>-1.905727346651723</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.836238899841391</v>
+        <v>-2.861106532844161</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.074658595597462</v>
+        <v>-3.099477376491926</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.218082539332357</v>
+        <v>-3.242805870914211</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.744302588922231</v>
+        <v>-3.768873322945836</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.672849675721856</v>
+        <v>-3.64920699904922</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.064866891638552</v>
+        <v>-1.052344601962929</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.558428082242564</v>
+        <v>-1.545518272666513</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.332178776416789</v>
+        <v>-1.319171644999187</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.388261047535991</v>
+        <v>-1.375281905137527</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7465580390056772</v>
+        <v>-0.7334472346307379</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6640561319405904</v>
+        <v>-0.6845204099645983</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.929647524787761</v>
+        <v>-1.916581270487285</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.23963832843431</v>
+        <v>-2.259349106318773</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.516616506108747</v>
+        <v>-2.536195694567311</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.271656443763916</v>
+        <v>-3.291108809905744</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.069679554668397</v>
+        <v>-3.089353470635281</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.002123876910602</v>
+        <v>-3.021844108602856</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.202015483949175</v>
+        <v>-3.221790022551289</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.355875763242331</v>
+        <v>-3.33702197826311</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.864679435573557</v>
+        <v>-1.852157145897934</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.671988423059418</v>
+        <v>-1.659078613483366</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.491127904541067</v>
+        <v>-1.507103142032832</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.907920723793524</v>
+        <v>-1.894941581395059</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.406954630331768</v>
+        <v>-1.393843825956829</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.518105416156388</v>
+        <v>-1.534106557809714</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.369122658332891</v>
+        <v>-2.356056404032415</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.260004732994204</v>
+        <v>-2.275779672887566</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.51119501963263</v>
+        <v>-2.526863930605089</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.003473533187346</v>
+        <v>-3.019147953720051</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.795132959842512</v>
+        <v>-2.810997633970153</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.060704100336665</v>
+        <v>-3.076425325077011</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.012434101156138</v>
+        <v>-3.028324728596267</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.447519450391631</v>
+        <v>-3.432120987774049</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.489028717074262</v>
+        <v>-1.47650642739864</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.120690522101221</v>
+        <v>-2.10778071252517</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.195959071143371</v>
+        <v>-2.208578554899034</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.604921624810373</v>
+        <v>-2.591942482411909</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.06491146733353</v>
+        <v>-2.051800662958591</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.428164410807227</v>
+        <v>-2.44070114312742</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.223309098455509</v>
+        <v>-3.235486606491143</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.419764941319798</v>
+        <v>-3.431972920719005</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.111539503848249</v>
+        <v>-3.123923476863489</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.493796391931255</v>
+        <v>-3.506216339219414</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.328549788726789</v>
+        <v>-3.341112078558275</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.268121450610387</v>
+        <v>-3.280714342661248</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.219391859937105</v>
+        <v>-3.232124491347321</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.534197912254733</v>
+        <v>-3.521438746036146</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.73922359083997</v>
+        <v>-1.749208713461179</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.484949793804503</v>
+        <v>-2.494941520226398</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.412846891991066</v>
+        <v>-2.42295872806028</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.815453439667763</v>
+        <v>-2.802474297269299</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.021725454029458</v>
+        <v>-2.008614649654518</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.233885327389672</v>
+        <v>-2.244100300303622</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.962007168458776</v>
+        <v>-2.971923292360579</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.272795132232126</v>
+        <v>-3.282676224611699</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.13277645579506</v>
+        <v>-3.142739454203998</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.292162545437606</v>
+        <v>-3.302236726693287</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.250797665647276</v>
+        <v>-3.260939661937257</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.103707334747078</v>
+        <v>-3.113915024568378</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.277464480538683</v>
+        <v>-3.287688750119891</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.538939399145512</v>
+        <v>-3.528368862391922</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.077580715031978</v>
+        <v>-1.08584930995206</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.020835486391547</v>
+        <v>-2.028995327481674</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.192188332078508</v>
+        <v>-2.200349833727557</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.547765158985186</v>
+        <v>-2.534786016586722</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.15501228498853</v>
+        <v>-2.141901480613591</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.119719785734894</v>
+        <v>-2.1279282606951</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.953039043121116</v>
+        <v>-2.960929573534564</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.07496816486222</v>
+        <v>-3.082892324017436</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.830985262830531</v>
+        <v>-2.839023872284322</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.132472501195601</v>
+        <v>-3.140535814933934</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.031649049348175</v>
+        <v>-3.039792872573756</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.935046341354443</v>
+        <v>-2.943229187698215</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.927474399579033</v>
+        <v>-2.935735973751235</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.306059934694005</v>
+        <v>-3.297443466607724</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2658</v>
+        <v>2659</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.369842814591998</v>
+        <v>-1.37646077033218</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.838245353931072</v>
+        <v>-1.844911112362219</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.02611752133005</v>
+        <v>-2.032770848180867</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.15823320431474</v>
+        <v>-2.145254061916276</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.077152584252737</v>
+        <v>-2.083843465086943</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.872422238383294</v>
+        <v>-1.879153689500299</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.500218550572598</v>
+        <v>-2.506730361520134</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.835196573246286</v>
+        <v>-2.841650583586059</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.688788525772054</v>
+        <v>-2.695310032786139</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.068389768177525</v>
+        <v>-3.074888981194469</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.689525933831597</v>
+        <v>-2.696199698108707</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.747778537252223</v>
+        <v>-2.754430059355684</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.809441105849821</v>
+        <v>-2.816131237183875</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.990925630366661</v>
+        <v>-2.983838766172774</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2842</v>
+        <v>2843</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.565242173099648</v>
+        <v>-1.570551884876089</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.967660846979413</v>
+        <v>-1.973012806610441</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.853543450846878</v>
+        <v>-1.858982828605498</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.704830873222228</v>
+        <v>-1.710311175840914</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.663573099646932</v>
+        <v>-1.669131466247656</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.698326082765441</v>
+        <v>-1.70384238699782</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.080387886839496</v>
+        <v>-2.085783019421456</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.529096934281483</v>
+        <v>-2.534390276325759</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.431110720370242</v>
+        <v>-2.436448643306768</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.665356631657346</v>
+        <v>-2.670711002543371</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.288947111567147</v>
+        <v>-2.294460111316013</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.552036016393117</v>
+        <v>-2.557456129473486</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.460967383186642</v>
+        <v>-2.466470164671364</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.649598159859515</v>
+        <v>-2.64376502885262</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.472357951303515</v>
+        <v>-1.476635490527769</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.551469923289552</v>
+        <v>-1.555870239540212</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.665338780838717</v>
+        <v>-1.669740065190119</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.583607065356532</v>
+        <v>-1.588026083947454</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.576914157591688</v>
+        <v>-1.581386978196853</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.393846639353221</v>
+        <v>-1.398355444953694</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.593030270769013</v>
+        <v>-1.597483749306214</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.108710760923557</v>
+        <v>-2.113039260915336</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.119164473677969</v>
+        <v>-2.123497712046778</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.324061921899464</v>
+        <v>-2.328407648622424</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.982301833444446</v>
+        <v>-1.986781804505505</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.293605915615494</v>
+        <v>-2.29798258037296</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.299194384621529</v>
+        <v>-2.303610265332757</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.395366178589008</v>
+        <v>-2.390590518731223</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3187</v>
+        <v>3188</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.118438320209968</v>
+        <v>-1.121965702511865</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.307262636519027</v>
+        <v>-1.310852123598181</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.52927401062761</v>
+        <v>-1.532825368309453</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.663965949452972</v>
+        <v>-1.667467626803628</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.528824692197951</v>
+        <v>-1.532410548451736</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.465066878416543</v>
+        <v>-1.468652749301818</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.658396231284904</v>
+        <v>-1.661929959541716</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.983695212819143</v>
+        <v>-1.987163805492528</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.028035064951403</v>
+        <v>-2.031496360046681</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.172050726719597</v>
+        <v>-2.175532064682386</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.921035524941544</v>
+        <v>-1.924612818122945</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.245900606300665</v>
+        <v>-2.249375627465341</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.335541001896623</v>
+        <v>-2.339021246779829</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.257037513125894</v>
+        <v>-2.253087448354876</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3320</v>
+        <v>3321</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.188307807158672</v>
+        <v>-1.191173978944668</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.28388348179368</v>
+        <v>-1.286821595545383</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.572831705516847</v>
+        <v>-1.575709042566899</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.696954834490654</v>
+        <v>-1.699788562903557</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.768967917188938</v>
+        <v>-1.771814794737423</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.635847169135218</v>
+        <v>-1.638717387774882</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.794829530947503</v>
+        <v>-1.797658862876247</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.185975494079329</v>
+        <v>-2.188717703421446</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.050591455928839</v>
+        <v>-2.053379768185998</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.012277130628604</v>
+        <v>-2.015131062176124</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.929922007205846</v>
+        <v>-1.932815038492286</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.240406856998014</v>
+        <v>-2.24320603149841</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.283063270929432</v>
+        <v>-2.2858772457936</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.107323501761947</v>
+        <v>-2.103994398801767</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.166260016690067</v>
+        <v>-1.168542220323801</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.031418859581159</v>
+        <v>-1.033821685052303</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.180019207900145</v>
+        <v>-1.182400203879908</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.409766115306553</v>
+        <v>-1.412075616496963</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.384074141068538</v>
+        <v>-1.386419292391302</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.128954082988486</v>
+        <v>-1.131359382159602</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.371641079826787</v>
+        <v>-1.373981846451478</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.62103792196708</v>
+        <v>-1.623331330584733</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.579799090399639</v>
+        <v>-1.582108800330786</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.604456029926737</v>
+        <v>-1.606802548584454</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.533031925731045</v>
+        <v>-1.535410724115238</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.801182669870322</v>
+        <v>-1.803483516702542</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.800347866666733</v>
+        <v>-1.802671393653192</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.824341007056809</v>
+        <v>-1.82162362810827</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3556</v>
+        <v>3557</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.9103618281954056</v>
+        <v>-0.9122885795539517</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.7698101394522538</v>
+        <v>-0.7718443483109851</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.8974135806174743</v>
+        <v>-0.8994295621648831</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.9764699076119996</v>
+        <v>-0.9784594104615181</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.9950052439746244</v>
+        <v>-0.9970130720949868</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9069030808161216</v>
+        <v>-0.9089243370333264</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.088829134966403</v>
+        <v>-1.090803989354711</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.344444170085119</v>
+        <v>-1.34636787022869</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.306084865104694</v>
+        <v>-1.308022970316593</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.214098409986086</v>
+        <v>-1.216098941013911</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.206752956399249</v>
+        <v>-1.208765227110298</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.353631280408599</v>
+        <v>-1.355601972261219</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.477318450291278</v>
+        <v>-1.479273071533662</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.521414059719319</v>
+        <v>-1.519162542299028</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3670</v>
+        <v>3671</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.8779075029414471</v>
+        <v>-0.8793959436722432</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6014812433317474</v>
+        <v>-0.6030985938669886</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7644826500941093</v>
+        <v>-0.7660695974352407</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.000062289772018</v>
+        <v>-1.001581806764314</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7629005841544938</v>
+        <v>-0.7645031352518572</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7770015642914458</v>
+        <v>-0.778591341337723</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.8470946491948865</v>
+        <v>-0.8486690272632487</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.136408557809737</v>
+        <v>-1.137920536097525</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.182707460225295</v>
+        <v>-1.184209705037276</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.092701775267777</v>
+        <v>-1.094257449573192</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.010229140642664</v>
+        <v>-1.011814898961696</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.260359008037028</v>
+        <v>-1.261876406256953</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.365989903337493</v>
+        <v>-1.367493302477833</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.428176395626238</v>
+        <v>-1.426344079818477</v>
       </c>
     </row>
     <row r="31">
@@ -5208,153 +5208,153 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3777</v>
+        <v>3778</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4881612753550968</v>
+        <v>-0.4893570751136167</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3177329677480003</v>
+        <v>-0.3190150523580684</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5664065109429472</v>
+        <v>-0.5676336033650955</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.659566773073017</v>
+        <v>-0.6607666329802768</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4442346704658178</v>
+        <v>-0.4455056495743079</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4230242217721383</v>
+        <v>-0.4242939463342879</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5727189373100785</v>
+        <v>-0.5739519225246639</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.840557207472898</v>
+        <v>-0.8417318976208676</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.8343117296432752</v>
+        <v>-0.835490260595229</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.7708190326143125</v>
+        <v>-0.7720365464049408</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6699366876358113</v>
+        <v>-0.6711867373819516</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.9119207000155782</v>
+        <v>-0.9131065325755543</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.052839128208042</v>
+        <v>-1.053998994696208</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.9737263650020509</v>
+        <v>-0.972361619030643</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 82.34</t>
+          <t>X &lt; 82.33</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>3875</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3329444930494816</v>
+        <v>-0.3204222033738588</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1559509607018938</v>
+        <v>-0.1430411511258427</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4854699346756064</v>
+        <v>-0.4981962052137447</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6759338134696335</v>
+        <v>-0.68869469681119</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5568643762004726</v>
+        <v>-0.5695002247606524</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4772047757637168</v>
+        <v>-0.4899151630130021</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.5222338557333757</v>
+        <v>-0.5091676014328996</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.6920266060618872</v>
+        <v>-0.6788455967666494</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.8936268795394184</v>
+        <v>-0.8804281405846552</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.8274514982081769</v>
+        <v>-0.8398262107203394</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.7858803775867145</v>
+        <v>-0.7724230838764967</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9693222081395376</v>
+        <v>-0.9558699194194276</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.065718538142583</v>
+        <v>-1.05216249179098</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.008100804521376</v>
+        <v>-1.018530440219529</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 84.82</t>
+          <t>X &lt; 84.81</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3975</v>
+        <v>3976</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1112918808920185</v>
+        <v>-0.1119012398600034</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.129591817799259</v>
+        <v>-0.1302164666272745</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3353046237146202</v>
+        <v>-0.335882788513743</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3922121997605572</v>
+        <v>-0.3927748073137778</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2895748266531584</v>
+        <v>-0.2901700383122403</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3048071360136859</v>
+        <v>-0.3053952135266726</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.4261290502602151</v>
+        <v>-0.426688005965147</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5028906425982314</v>
+        <v>-0.5034363116701357</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.650659465147875</v>
+        <v>-0.651169056844104</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6577153201125583</v>
+        <v>-0.6582337938797451</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.6474319592487277</v>
+        <v>-0.6479558091265574</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.7247835340288091</v>
+        <v>-0.7252878153450766</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.8292636893387098</v>
+        <v>-0.8297471225094597</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.7667536752862389</v>
+        <v>-0.7660283307887497</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4037</v>
+        <v>4038</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1971420239136776</v>
+        <v>-0.1975292124647439</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04228039452271304</v>
+        <v>-0.04271940754879466</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1767581101265563</v>
+        <v>-0.1771674080815515</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.181339886703725</v>
+        <v>-0.1817471789941081</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1626211394376682</v>
+        <v>-0.1630377448929252</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1730295286483781</v>
+        <v>-0.1734412980129107</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.2195739340374061</v>
+        <v>-0.2199751127573961</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.3270057210039781</v>
+        <v>-0.327384434305074</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.34969894756739</v>
+        <v>-0.3500727598961291</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.3448689668345679</v>
+        <v>-0.3452512661992841</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3873131871905215</v>
+        <v>-0.3876868979616077</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.5371610055547009</v>
+        <v>-0.5374975431051823</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.5473842004190672</v>
+        <v>-0.547721912311907</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.5314709212640878</v>
+        <v>-0.5309751189969489</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1113225127337927</v>
+        <v>-0.1115950730355735</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.07387369732429505</v>
+        <v>0.07354654486016443</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.01442476101257029</v>
+        <v>-0.01473274588988005</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.006900610196090895</v>
+        <v>0.006588007760200298</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.02910521526556664</v>
+        <v>-0.02941224548891341</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.01178095281728275</v>
+        <v>-0.01209066738907438</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1076233498469179</v>
+        <v>-0.1079102553194176</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1943398574996991</v>
+        <v>-0.1946083671775583</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2174038357155226</v>
+        <v>-0.2176671917071644</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2460289913724836</v>
+        <v>-0.2462903557589158</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2411747673235638</v>
+        <v>-0.2414386360836573</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3645482911322731</v>
+        <v>-0.3647818879981628</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.4035533380370779</v>
+        <v>-0.4037799277490919</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3606308487971503</v>
+        <v>-0.3602920261685725</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/rsi/rsi_14.xlsx
+++ b/workspaces/btc_daily_14days/rsi/rsi_14.xlsx
@@ -568,521 +568,521 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 19.13</t>
+          <t>X ≈ 19.16</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.89860365244412</v>
+        <v>9.364548802337694</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11.72672530023624</v>
+        <v>10.16231563554154</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>11.33581353657102</v>
+        <v>9.772039949976516</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.035395230024193</v>
+        <v>9.903892850536892</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6.066927480752319</v>
+        <v>7.042489604599275</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.497057103396102</v>
+        <v>2.564208788197107</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-5.891468734819611</v>
+        <v>-4.626159568333158</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.923856149107287</v>
+        <v>-2.714976224540443</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.8863844466006157</v>
+        <v>-0.3744587792589016</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.399042597446766</v>
+        <v>-3.576126626665648</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.478682990643925</v>
+        <v>-8.53944600991499</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-9.884063554145435</v>
+        <v>-8.483488670392276</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-15.18347494215332</v>
+        <v>-13.6414484371074</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-17.4005918092192</v>
+        <v>-15.77679281736453</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 21.61</t>
+          <t>X ≈ 21.63</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.870373952659456</v>
+        <v>9.913652785246086</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.503778206725087</v>
+        <v>4.47127008457668</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.873852655206363</v>
+        <v>7.909256718750321</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.769331048749116</v>
+        <v>9.963018771715554</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5.46970031226536</v>
+        <v>5.629130007996885</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.651229279384495</v>
+        <v>6.950916835459317</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>9.452290981566307</v>
+        <v>8.812040794023901</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>12.75619915394632</v>
+        <v>12.18949378023132</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.929659915477643</v>
+        <v>10.23499994741992</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>6.198009500684833</v>
+        <v>7.493474072043384</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.109604277345532</v>
+        <v>5.369684688293056</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.030759440592881</v>
+        <v>5.429067389642874</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>7.498455102569622</v>
+        <v>6.957875566727765</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>7.725961343102803</v>
+        <v>7.208555167982368</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 24.09</t>
+          <t>X ≈ 24.11</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1.424458842819696</v>
+        <v>1.244994944241483</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.725266077079077</v>
+        <v>7.277097282436415</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11.31663493618775</v>
+        <v>12.63142383878166</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>5.469973058844282</v>
+        <v>7.013280760290407</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.902619781826324</v>
+        <v>10.34544963839222</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.217648571427219</v>
+        <v>4.862367051864155</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.868452550968108</v>
+        <v>0.08422643679433151</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-1.352855216481892</v>
+        <v>-1.252083522876767</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.576346264367288</v>
+        <v>2.552096608073555</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.311014348393627</v>
+        <v>-2.112362168680036</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.471105128013491</v>
+        <v>1.526354218595486</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-2.4927879580829</v>
+        <v>-2.259409976493579</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.209362537372513</v>
+        <v>1.190063398431008</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.575017946876329</v>
+        <v>-0.4837525243253182</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 26.57</t>
+          <t>X ≈ 26.59</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8.424998308937603</v>
+        <v>7.469918443650137</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.431404968656388</v>
+        <v>4.562160062722505</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.50284619283949</v>
+        <v>9.492497362532532</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.902753268602062</v>
+        <v>6.962833775632689</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>4.624197558721235</v>
+        <v>3.813754330106853</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>6.292037017487914</v>
+        <v>5.417731411889577</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.469035509449704</v>
+        <v>2.694887994858078</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.997112127737701</v>
+        <v>2.229760107706703</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1970775458587894</v>
+        <v>-0.4697443593745803</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.44120911818473</v>
+        <v>2.703252657698485</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.245451065547357</v>
+        <v>-2.829274624983981</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.436046302090055</v>
+        <v>-2.771922832554061</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.4863341417054485</v>
+        <v>-1.834803300902806</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2605984914776727</v>
+        <v>-0.2529832935554879</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 29.05</t>
+          <t>X ≈ 29.06</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>136</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-10.54198898024576</v>
+        <v>-9.837811571691546</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.349655585248883</v>
+        <v>-2.617252296944251</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.543644324878869</v>
+        <v>-0.8101215885481636</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.05398925716937697</v>
+        <v>0.7873785223097443</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.719217117479758</v>
+        <v>2.501768097202508</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.9202189181730915</v>
+        <v>-0.1620297558449408</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.004784105137489</v>
+        <v>-0.2222307937000068</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-7.349365683098043</v>
+        <v>-6.560237458461515</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.472609690898899</v>
+        <v>-3.661512897541783</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-8.263852091816915</v>
+        <v>-8.15780692471769</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.059062649450695</v>
+        <v>-3.220979644151619</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.759978614742096</v>
+        <v>-3.898679280091422</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.386011820996011</v>
+        <v>-6.500189334717199</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.954393817828972</v>
+        <v>-4.78239505826231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 31.53</t>
+          <t>X ≈ 31.54</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.013041024393679</v>
+        <v>0.5701335673307995</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.944095204415916</v>
+        <v>-3.340898872162647</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.120050751448836</v>
+        <v>-5.283262828343211</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.43001782708474</v>
+        <v>-2.058164008703855</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.412191003982443</v>
+        <v>-1.002891450896662</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.016894561677411</v>
+        <v>-4.600877948590174</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.982688425387245</v>
+        <v>-1.566921429826273</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.674451935347008</v>
+        <v>-1.263051578159669</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.860601855032968</v>
+        <v>-4.74264016270179</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.37730270709703</v>
+        <v>-2.469203296429939</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-4.702445002390846</v>
+        <v>-4.997675590797577</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.581933149963945</v>
+        <v>1.257089557689753</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.525717703349997</v>
+        <v>-3.787628143212459</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-4.081232053122754</v>
+        <v>-4.314998797432416</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 34.01</t>
+          <t>X ≈ 34.02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.075757858226822</v>
+        <v>-1.335980568719783</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-5.280369749755721</v>
+        <v>-5.304608889944006</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.474687744727873</v>
+        <v>-6.492885436659975</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.353451547815396</v>
+        <v>-2.400480063456669</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.49356304663641</v>
+        <v>7.047428488134678</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6.195218810822787</v>
+        <v>5.735428144969163</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.714562009815403</v>
+        <v>3.297513798893647</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.449399506810678</v>
+        <v>2.040162210122823</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.589328481505703</v>
+        <v>1.210915865803344</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.7397561558689887</v>
+        <v>0.3885894990662351</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.2649450023913857</v>
+        <v>-0.6083597055576107</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.169433149964306</v>
+        <v>1.828899842344931</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.949282296651255</v>
+        <v>5.401404462789252</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.775017946877249</v>
+        <v>7.239080198507764</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 36.48</t>
+          <t>X ≈ 36.49</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.07191754872791</v>
+        <v>-1.67818140351482</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.555231692333876</v>
+        <v>-0.9959236298647909</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.786949380407954</v>
+        <v>-4.245280591428461</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.954655589513962</v>
+        <v>-2.970434329392837</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.08958424845006618</v>
+        <v>-0.6066398138579032</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-3.198889486374725</v>
+        <v>-2.619908611182602</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-2.150340427146581</v>
+        <v>-1.54176016511569</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.058109951131371</v>
+        <v>3.693668532869687</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.996763821327441</v>
+        <v>3.654584612343037</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.462483428596137</v>
+        <v>2.571056377299229</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.014945002391201</v>
+        <v>-0.1642162587100913</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.116930486399511</v>
+        <v>-1.248670065339972</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.241626794258501</v>
+        <v>-3.929226747699346</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.1749820531228892</v>
+        <v>-0.8244118649846612</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 38.96</t>
+          <t>X ≈ 38.97</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>159</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-4.67016320616294</v>
+        <v>-4.702321418263111</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.024115008954638</v>
+        <v>-5.02857250472762</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.536649462943409</v>
+        <v>-3.539129891718396</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7.175889701002177</v>
+        <v>-7.180833744872842</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-7.088214464522906</v>
+        <v>-7.041751240159293</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.907479841630284</v>
+        <v>-4.883625191818858</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-9.39325431345555</v>
+        <v>-9.342372405688145</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-6.090789033514106</v>
+        <v>-6.037754502045317</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.153721274216245</v>
+        <v>-6.074525515542803</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-5.116847617715912</v>
+        <v>-5.012207184280342</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.692617958365901</v>
+        <v>-4.587583995495521</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-5.916101441230843</v>
+        <v>-5.788349262319414</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-6.336252294544252</v>
+        <v>-6.1853270280427</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-9.884101549978098</v>
+        <v>-9.712102790411436</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 41.44</t>
+          <t>X ≈ 41.45</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>167</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>8.57461580893402</v>
+        <v>8.551077278171441</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5.775341382362456</v>
+        <v>5.777813423344924</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.992555941499582</v>
+        <v>2.99422380840852</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.329817225229448</v>
+        <v>1.330117811510291</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.987934686414143</v>
+        <v>2.037236679384399</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>7.670241583933326</v>
+        <v>7.694109533218871</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.194810677811873</v>
+        <v>5.241132747739265</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>8.321027351870057</v>
+        <v>8.36481933523222</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7.06512405399539</v>
+        <v>7.13167040406865</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.616402862455949</v>
+        <v>5.710823913534867</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>7.208108889824366</v>
+        <v>7.301730670135733</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>5.446079856550945</v>
+        <v>5.566652481377851</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.025929003237671</v>
+        <v>5.173286035848456</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1375569034220234</v>
+        <v>0.0344418561445039</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>195</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.729991622560973</v>
+        <v>-2.517856369936446</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-7.406682871372197</v>
+        <v>-7.180991620862123</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-9.338366007126822</v>
+        <v>-9.115687502443343</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-12.7952020890634</v>
+        <v>-12.80498871898845</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-12.82611745945508</v>
+        <v>-12.78207765296942</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-12.53310363730262</v>
+        <v>-12.50929213415049</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-13.13418255923909</v>
+        <v>-13.0815308709827</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-16.16920149403445</v>
+        <v>-16.10856173828173</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-14.18468402216024</v>
+        <v>-14.09613547287114</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-14.52178230566958</v>
+        <v>-14.40632385084475</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-14.21366295110915</v>
+        <v>-14.0977987269666</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-16.23056685003588</v>
+        <v>-16.09483901817806</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-15.11225616488786</v>
+        <v>-14.95784138912494</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-11.29677692491762</v>
+        <v>-11.12477816535096</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-8.040583247348195</v>
+        <v>-7.774938519586499</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-6.436321916453281</v>
+        <v>-6.389424459603596</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.75345700045802</v>
+        <v>-1.972530193210524</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.699514030724302</v>
+        <v>-0.9304710143693882</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-4.475579243202084</v>
+        <v>-4.612500804656229</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.4779501314046257</v>
+        <v>-0.6910147353317555</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.699035789487013</v>
+        <v>-1.663007623971055</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.872358097920639</v>
+        <v>-5.777163682664543</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-6.599213936690042</v>
+        <v>-6.726101844874542</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-6.060243844130909</v>
+        <v>-6.18011679355682</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.024204261650453</v>
+        <v>-3.191225090294346</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.600937220406252</v>
+        <v>-1.76617004659618</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.2937267410951563</v>
+        <v>-0.3366955458482082</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.332389460530159</v>
+        <v>-1.915083750177097</v>
       </c>
     </row>
     <row r="18">
@@ -1199,98 +1199,98 @@
         <v>218</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-7.752640820376158</v>
+        <v>-7.792620655339697</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.504400430752668</v>
+        <v>-2.508624205897668</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.901313796189875</v>
+        <v>-2.902943475240498</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-5.724184028186016</v>
+        <v>-5.981044030680636</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.265223354116529</v>
+        <v>-6.470729132403939</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-7.804982551265489</v>
+        <v>-8.030081187053881</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-5.596710319970249</v>
+        <v>-6.260634186408424</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.397049313296726</v>
+        <v>-2.604012086229353</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.458031469819502</v>
+        <v>-2.642001937165233</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.014372284497981</v>
+        <v>-1.17914623731216</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7603578464279011</v>
+        <v>-0.9253976117378002</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.478273272054231</v>
+        <v>-3.808229998114918</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.604846143716159</v>
+        <v>-1.454554547001621</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.13140407147138</v>
+        <v>-3.959405311904717</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 51.35</t>
+          <t>X ≈ 51.36</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.765245853502392</v>
+        <v>1.734883466206419</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-6.003742840470608</v>
+        <v>-5.973116133103844</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-8.296718816439302</v>
+        <v>-8.251721372862995</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-8.640792501629626</v>
+        <v>-8.59289477602325</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-7.763407877163715</v>
+        <v>-7.668254425661864</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-10.31316327787173</v>
+        <v>-10.22316820522586</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-10.87544515665616</v>
+        <v>-10.75436379124518</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-13.44318175383761</v>
+        <v>-13.57616108956937</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-8.29089376818019</v>
+        <v>-8.429031599044571</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-7.719011616642966</v>
+        <v>-7.83793479338474</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.923712774903052</v>
+        <v>-8.041995556677684</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-5.045732726813135</v>
+        <v>-5.156129520929873</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.991949930837549</v>
+        <v>-5.083309455091374</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.292280631321802</v>
+        <v>-4.366190840725906</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>212</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-4.398505761555775</v>
+        <v>-4.433766039488582</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-6.235744075551473</v>
+        <v>-6.511155607317356</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.479883064800994</v>
+        <v>-5.021632808600245</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-4.820573165404959</v>
+        <v>-5.366095629941974</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.591111912801999</v>
+        <v>-2.081759865233629</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3522808693575357</v>
+        <v>-0.8664610364492233</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.4369912286236044</v>
+        <v>-0.9355048319459129</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.847456098825539</v>
+        <v>-2.350472775666724</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.32353259497107</v>
+        <v>-3.800773891527129</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.343262712055328</v>
+        <v>-1.805891706941786</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.491360096730716</v>
+        <v>-2.482613184135147</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.513585717960517</v>
+        <v>-1.480167303905432</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.820529024104005</v>
+        <v>-3.954505012330578</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.594793373877472</v>
+        <v>-3.422794614310696</v>
       </c>
     </row>
     <row r="21">
@@ -1355,202 +1355,202 @@
         <v>218</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>5.771616669713666</v>
+        <v>5.746768909057963</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.789070010478206</v>
+        <v>2.78744503491145</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1036550561561143</v>
+        <v>0.1001290649452073</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.2343071962965482</v>
+        <v>0.2300131061598876</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.51523243186017</v>
+        <v>-3.470245209103851</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.927839117583261</v>
+        <v>-0.9038817086334916</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.847411862170588</v>
+        <v>-2.799400183180211</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.020902524305896</v>
+        <v>-0.9716549619122787</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.294262108162151</v>
+        <v>0.3675192179418474</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.473087880828359</v>
+        <v>-1.37374055553358</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.7603578464280005</v>
+        <v>-0.6604498104092258</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.184695290402637</v>
+        <v>-1.060998669374605</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.6887318379350162</v>
+        <v>0.8374213857128439</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9203948971594542</v>
+        <v>-0.7483961375929979</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 58.79</t>
+          <t>X ≈ 58.78</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-5.03527590931197</v>
+        <v>-5.03536435013951</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4411980185581541</v>
+        <v>0.4521656354116459</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.04409919487368086</v>
+        <v>0.05842764709706927</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.708900986339316</v>
+        <v>2.713564213564268</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.383343818577906</v>
+        <v>-1.311038462741301</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.23999956355113</v>
+        <v>0.9819490762796477</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.185746057076955</v>
+        <v>2.941495007256322</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.180606347300305</v>
+        <v>-0.0495902783796609</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.8956042356184639</v>
+        <v>-1.096663897617411</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.253137245146242</v>
+        <v>-2.425542983483012</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.603075302177324</v>
+        <v>1.410720609385052</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.3930033982593386</v>
+        <v>-0.551314673452076</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.320768464770495</v>
+        <v>-1.451523105066407</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9354240382478096</v>
+        <v>0.8177237771510946</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 61.27</t>
+          <t>X ≈ 61.26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-4.409957316129109</v>
+        <v>-5.257364572139792</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.862016436514786</v>
+        <v>-3.543838360592346</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.631270803697781</v>
+        <v>-0.09142250275320407</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.565122501626639</v>
+        <v>3.884615384615316</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>4.344192516922121</v>
+        <v>3.395366243663524</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.837218720470247</v>
+        <v>0.3714484657790322</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.013377926421349</v>
+        <v>3.058045123806316</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.915874500025971</v>
+        <v>1.493311264521999</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.31141408263376</v>
+        <v>0.3574375564840437</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.178886590651594</v>
+        <v>2.280861722921813</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.517663693260971</v>
+        <v>2.62617182483627</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2911722803989036</v>
+        <v>-0.6123647345021368</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.588412731433316</v>
+        <v>1.739730086186789</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>2.270670120790292</v>
+        <v>1.439324398751594</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 63.75</t>
+          <t>X ≈ 63.74</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.005271814769578498</v>
+        <v>0.7507577403305348</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>5.023919975849338</v>
+        <v>4.602363263870267</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.31423146402247</v>
+        <v>2.03471223207724</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.339484231920288</v>
+        <v>1.077639751552795</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1988053211755343</v>
+        <v>0.5883906106008752</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.413485835531503</v>
+        <v>3.578567433767752</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.091206415491861</v>
+        <v>6.778780909759554</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.519165396014451</v>
+        <v>4.682513366767516</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.800724675955699</v>
+        <v>3.558584235891594</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.055778255316511</v>
+        <v>3.821712176815737</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>2.851077097056319</v>
+        <v>3.617571729279646</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.780482873721027</v>
+        <v>2.588781944905413</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.2553596447170747</v>
+        <v>1.106667496602519</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.586067670634151</v>
+        <v>2.442668880356955</v>
       </c>
     </row>
     <row r="25">
@@ -1563,514 +1563,514 @@
         <v>164</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.445913237758262</v>
+        <v>5.416717443405631</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.2249710471336</v>
+        <v>3.223784260688944</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.000931369695564</v>
+        <v>1.000777979691243</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-3.137136169642908</v>
+        <v>-3.137630662020911</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6266452349337186</v>
+        <v>-0.5780993151679468</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.768295595542604</v>
+        <v>-2.744338186592991</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.853005954808772</v>
+        <v>-2.804994275818451</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.3384619867704757</v>
+        <v>0.3877095491641924</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.3322762673132758</v>
+        <v>-0.2590191575335794</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.6470732290397194</v>
+        <v>0.7464205543342928</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.7771401243424165</v>
+        <v>-0.6772320883237413</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.352518069548069</v>
+        <v>-1.228821448519824</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.992181117983506</v>
+        <v>-2.843491570205678</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.2823350200479737</v>
+        <v>0.4543337796146361</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 68.7</t>
+          <t>X ≈ 68.69</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>133</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-2.856855880158413</v>
+        <v>-2.886051674511044</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.7086434769817274</v>
+        <v>-0.7098302634263831</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.607174260233002</v>
+        <v>-2.607327650237323</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.476949116644555</v>
+        <v>-2.477443609022558</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-7.526516865228977</v>
+        <v>-7.477970945463206</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.725383437097733</v>
+        <v>-5.70142602814812</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-5.058214097115609</v>
+        <v>-5.010202418125289</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-7.029042139398761</v>
+        <v>-6.979794577005045</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.578746100432731</v>
+        <v>-2.505488990653035</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.834492997974337</v>
+        <v>1.93384032326891</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-2.129606656526541</v>
+        <v>-2.029698620507865</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.095228504171217</v>
+        <v>-1.971531883142973</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.011619958988298</v>
+        <v>-0.8629304112104705</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.469754788982513</v>
+        <v>1.641753548549175</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 71.18</t>
+          <t>X ≈ 71.17</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>133</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.6012167824140491</v>
+        <v>-0.6304125767666804</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.306394117003322</v>
+        <v>5.305207330558666</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>8.671021228489018</v>
+        <v>8.670867838484696</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.793727575084766</v>
+        <v>5.793233082706763</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>8.26295681898155</v>
+        <v>8.311502738747322</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>11.5678496456092</v>
+        <v>11.59180705455881</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.227500188598597</v>
+        <v>9.275511867588918</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>12.51983004105245</v>
+        <v>12.56907760344617</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10.20320878678523</v>
+        <v>10.27646589656492</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.601410291207216</v>
+        <v>8.700757616501789</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.396709132947137</v>
+        <v>8.496617168965813</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.182966984550596</v>
+        <v>9.306663605578841</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>10.26657552973333</v>
+        <v>10.41526507751116</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.229153285223063</v>
+        <v>5.401152044789725</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 73.66</t>
+          <t>X ≈ 73.65</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>7.713258726747199</v>
+        <v>7.293809743740468</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>8.0438202064989</v>
+        <v>8.651809129172847</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>8.619922608151583</v>
+        <v>9.238463297720827</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>13.60451668377883</v>
+        <v>13.2899159663865</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>12.09535334427537</v>
+        <v>12.80066682543464</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.567484655463851</v>
+        <v>7.191099403077089</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>8.424521869013226</v>
+        <v>9.091227627577112</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>7.957453225226487</v>
+        <v>8.625394867193769</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.896471068703711</v>
+        <v>8.588422258056973</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>11.90092120441274</v>
+        <v>12.66655446155578</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9.754472473337017</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>13.67234577132334</v>
+        <v>13.50097290824727</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.368699772378932</v>
+        <v>9.184246354232464</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>8.623561636197699</v>
+        <v>8.452899059385139</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 76.14</t>
+          <t>X ≈ 76.12</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>114</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.1506629168340652</v>
+        <v>0.9986601049375778</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.679827700963273</v>
+        <v>3.801447932062473</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.407863333752047</v>
+        <v>2.530516961291582</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.725069417396384</v>
+        <v>-1.725563909774387</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.508570854069276</v>
+        <v>6.557116773835091</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>3.297172953879802</v>
+        <v>3.321130362829457</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>6.721234524438195</v>
+        <v>6.769246203428516</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5.37697289819527</v>
+        <v>4.549027478132842</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2.684411794304062</v>
+        <v>2.757668904083815</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>2.711685980430403</v>
+        <v>2.811033305725019</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>5.138563769538628</v>
+        <v>4.361278823101159</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.66416999206939</v>
+        <v>1.787866613097634</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>2.121212121212125</v>
+        <v>2.269901668989952</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.469754788982556</v>
+        <v>1.641753548549175</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 78.62</t>
+          <t>X ≈ 78.6</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>107</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>12.93964471712919</v>
+        <v>12.91044892277656</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>9.459299745560649</v>
+        <v>9.458112959115994</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.260790043048623</v>
+        <v>6.260636653044322</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>11.06391238289861</v>
+        <v>11.06341789052068</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>10.52562282980299</v>
+        <v>9.639589310316389</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>11.75757629869042</v>
+        <v>10.84695426838765</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>8.869127621667218</v>
+        <v>7.982559861405221</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.336638417132868</v>
+        <v>9.385885979526584</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>11.1448151391148</v>
+        <v>10.28349280964209</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>10.29489634278488</v>
+        <v>9.459664228827066</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>11.02477462377693</v>
+        <v>11.12468265979567</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>11.0591527761324</v>
+        <v>11.18284939716059</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>9.704422483566603</v>
+        <v>9.853112031344374</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>14.60305533005477</v>
+        <v>14.77505408962143</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 81.09</t>
+          <t>X ≈ 81.08</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>6.281970567403796</v>
+        <v>5.653153481235464</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>6.732640144443053</v>
+        <v>7.131200885875529</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.214157419481865</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.779328777135937</v>
+        <v>-1.295918367346914</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.410401835386324</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.051172135648152</v>
+        <v>-2.532790152745235</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.018756680343451</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.67539937676289</v>
+        <v>6.124394467033731</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.633005460172313</v>
+        <v>-2.075843448225562</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-3.482924256502137</v>
+        <v>-2.899672029040516</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.718553249813851</v>
+        <v>-4.124220639841887</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.622319427355492</v>
+        <v>-2.025237575946385</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.9806146105658371</v>
+        <v>-0.3795791759795577</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.81673463044234</v>
+        <v>-2.171350640494808</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 83.57</t>
+          <t>X ≈ 83.56</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>101</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>7.915123573426044</v>
+        <v>7.885927779073413</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.3633434209562907</v>
+        <v>0.3621566345116349</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.909166095607176</v>
+        <v>5.909012705602855</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.98988628870048</v>
+        <v>10.98939179632248</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>10.4515967356048</v>
+        <v>10.50014265537057</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.788574725635932</v>
+        <v>6.812532134585545</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.743468326765807</v>
+        <v>2.791480005756128</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>6.236795722583011</v>
+        <v>6.286043284976728</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>8.156011585862274</v>
+        <v>8.22926869564197</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.31599377963137</v>
+        <v>6.415341104925943</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>4.131094601569195</v>
+        <v>4.231002637587871</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.125868793528419</v>
+        <v>8.249565414556663</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>7.705717940215095</v>
+        <v>7.854407487992923</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.921552600342615</v>
+        <v>9.093551359909277</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 86.05</t>
+          <t>X ≈ 86.03</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>62</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-5.706722482147228</v>
+        <v>-5.735918276499859</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.585317231240531</v>
+        <v>5.584130444795875</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.02925552390484</v>
+        <v>10.02910213390052</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>13.38528711910609</v>
+        <v>13.38479262672809</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.008287888591063</v>
+        <v>8.056833808356835</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.305661918226122</v>
+        <v>8.329619327175735</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>13.05966123637928</v>
+        <v>13.1076729153696</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>10.97968936678614</v>
+        <v>11.02893692917986</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>18.98322333929558</v>
+        <v>19.05648044907527</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>19.74620776877222</v>
+        <v>19.8455550940668</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>16.31570015889912</v>
+        <v>16.41560819491779</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>11.51136863383514</v>
+        <v>11.63506525486338</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>17.54283068374744</v>
+        <v>17.69152023152527</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>14.5427598823611</v>
+        <v>14.71475864192777</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 88.53</t>
+          <t>X ≈ 88.51</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>43</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>7.98420024853538</v>
+        <v>7.955004454182749</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>11.02417694616923</v>
+        <v>11.02299015972458</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>15.28056835211189</v>
+        <v>15.28041496210757</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>17.73637489104909</v>
+        <v>17.73588039867109</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>12.54692254725574</v>
+        <v>12.59546846702151</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>15.16987797223966</v>
+        <v>15.19383538118927</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.43400482227585</v>
+        <v>10.48201650126617</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>12.29251757383792</v>
+        <v>12.34176513623164</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>12.23153541731513</v>
+        <v>12.30479252709483</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>9.056035225636435</v>
+        <v>9.155382550931009</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>13.50249685807391</v>
+        <v>13.60240489409259</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>15.86245640577807</v>
+        <v>15.98615302680631</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>13.1167241571158</v>
+        <v>13.26541370489362</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>15.66804120269114</v>
+        <v>15.8400399622578</v>
       </c>
     </row>
   </sheetData>
@@ -2210,573 +2210,573 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 17.89</t>
+          <t>X &gt; 17.92</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4081</v>
+        <v>4092</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.01389111602531301</v>
+        <v>-0.01315689187845948</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.0002506738608971659</v>
+        <v>0.0002783414191540601</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.03917067355361326</v>
+        <v>-0.03906199462856819</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.09118759722635872</v>
+        <v>-0.09093125304730165</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1027618787407505</v>
+        <v>-0.1036463263074054</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.01236518978871715</v>
+        <v>0.01175937438269159</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.06332262139290634</v>
+        <v>0.06200481378705547</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.09900553054692551</v>
+        <v>0.09756206496600583</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1983876296339986</v>
+        <v>0.1961026746219474</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2922653357955483</v>
+        <v>0.2891034811635649</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2972489251308446</v>
+        <v>0.2940594927239317</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.2964965837138109</v>
+        <v>0.2927389551643316</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2821583378070116</v>
+        <v>0.2778399118607453</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.276806724137721</v>
+        <v>0.2963813203246559</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 20.37</t>
+          <t>X &gt; 20.39</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4040</v>
+        <v>4050</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.124636731249872</v>
+        <v>-0.1104071731518133</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.1187556280404323</v>
+        <v>-0.1051057490384011</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.154609869745471</v>
+        <v>-0.1408067555355785</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1838088585920161</v>
+        <v>-0.1945812807881779</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1653750628346131</v>
+        <v>-0.1777544026279188</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.002702228146411301</v>
+        <v>-0.01471047139019532</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1237549099089179</v>
+        <v>0.1106228147868293</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1398316020483676</v>
+        <v>0.1267291287090373</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1914054837192509</v>
+        <v>0.2020196082177534</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.3195781143259708</v>
+        <v>0.3291873489484658</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.3761630856622276</v>
+        <v>0.3856662164550073</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.3998141494693144</v>
+        <v>0.3837516860960264</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.4391115468363083</v>
+        <v>0.4221880873315342</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.4562060656891234</v>
+        <v>0.4630660891599589</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 22.85</t>
+          <t>X &gt; 22.87</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3987</v>
+        <v>3998</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2309160305343525</v>
+        <v>-0.2407851415952109</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1536175024428914</v>
+        <v>-0.1646283961989852</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2347474453217089</v>
+        <v>-0.2455099322896785</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3161179669665088</v>
+        <v>-0.3266961388997842</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.240283263205896</v>
+        <v>-0.2532816635965318</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1044474927310972</v>
+        <v>-0.1053089256063515</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.0002512129398013485</v>
+        <v>-0.002552206453877659</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02788033179928817</v>
+        <v>-0.03016525895458244</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.07524609448342545</v>
+        <v>0.07152561681242275</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.2414349331178016</v>
+        <v>0.2360050303889523</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.3265336943506583</v>
+        <v>0.3208415639948825</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.3249608511423645</v>
+        <v>0.3181297709923712</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3452702605423852</v>
+        <v>0.3371816468791522</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3595677336843721</v>
+        <v>0.3753308635224499</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 25.33</t>
+          <t>X &gt; 25.35</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3937</v>
+        <v>3946</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2519393334725493</v>
+        <v>-0.2603646054734412</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.2790795748269659</v>
+        <v>-0.2626947254663534</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3814502949725735</v>
+        <v>-0.4152008993691751</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3896014699613062</v>
+        <v>-0.4234216327563161</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.35639836410801</v>
+        <v>-0.3929507025482266</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.1466381971273165</v>
+        <v>-0.1707724711786867</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.01077496610552231</v>
+        <v>-0.003695766881882889</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.01105311710938395</v>
+        <v>-0.01406294022068977</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.04348205879783507</v>
+        <v>0.03883689619772923</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2738511038253293</v>
+        <v>0.2669515824293853</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.3119976080709677</v>
+        <v>0.3049554367675071</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.3607463325904874</v>
+        <v>0.3520963363419085</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.3215962412786055</v>
+        <v>0.3259424550188612</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.3441314851043273</v>
+        <v>0.3866517799360523</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 27.81</t>
+          <t>X &gt; 27.82</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3864</v>
+        <v>3871</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4158669856195374</v>
+        <v>-0.4101375914419947</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.3869639877861459</v>
+        <v>-0.3561755079809856</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.5870801199234705</v>
+        <v>-0.6071609535264031</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.5462634513058049</v>
+        <v>-0.5665291387313118</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.4504934734161097</v>
+        <v>-0.4744549333539965</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.2682798354986673</v>
+        <v>-0.2790488316101332</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.05455966631273412</v>
+        <v>-0.05598039156038226</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.06788439632103405</v>
+        <v>-0.05753664949337178</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.04058028070377162</v>
+        <v>0.04869057591044168</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2140123007590233</v>
+        <v>0.2197486424538866</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3603137967806376</v>
+        <v>0.3656806381705877</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.3946919491359608</v>
+        <v>0.4126237033445506</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.3368599364022629</v>
+        <v>0.3678065551723435</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.3555562491546738</v>
+        <v>0.3990446062114046</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 30.29</t>
+          <t>X &gt; 30.3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3728</v>
+        <v>3735</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.04645910169540457</v>
+        <v>-0.06685414798445066</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.2788829638443673</v>
+        <v>-0.273844465598394</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.5521840008585741</v>
+        <v>-0.599770686762561</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5681610823016783</v>
+        <v>-0.6158280522257016</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5296460057020127</v>
+        <v>-0.5828261066219156</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2444966500792063</v>
+        <v>-0.2833097671667844</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.01989482626976979</v>
+        <v>-0.04992682939412418</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1977490411794065</v>
+        <v>0.179241746763573</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2052245500540835</v>
+        <v>0.183787676951809</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5232906155096444</v>
+        <v>0.5247948424901239</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.5215356843040837</v>
+        <v>0.4962792455054839</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5827378709941655</v>
+        <v>0.5696082296490417</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6185956013717373</v>
+        <v>0.6178861913236133</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5492668739158759</v>
+        <v>0.5877128242484631</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 32.77</t>
+          <t>X &gt; 32.78</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3600</v>
+        <v>3606</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.08413021728969028</v>
+        <v>-0.08964156209306395</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.1841198619573845</v>
+        <v>-0.1641245492237999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.4253265163931488</v>
+        <v>-0.4322247948424547</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5019617313760634</v>
+        <v>-0.5642303433001103</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.4982666279853802</v>
+        <v>-0.5677988106120893</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.07481139100016065</v>
+        <v>-0.1288543330559619</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.04989339058774078</v>
+        <v>0.004341696245290905</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2643161870114596</v>
+        <v>0.2308379306002522</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3853428222349535</v>
+        <v>0.3600242802006477</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.661978378091213</v>
+        <v>0.6319012650970777</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7072772198310204</v>
+        <v>0.6928183952234832</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.5472109277419079</v>
+        <v>0.5450144716575593</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.7659489633173848</v>
+        <v>0.7754877856539366</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.7139068357661316</v>
+        <v>0.7631010103817957</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 35.24</t>
+          <t>X &gt; 35.26</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3475</v>
+        <v>3480</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.0124889352415849</v>
+        <v>-0.04451549461175119</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.0008015206696754262</v>
+        <v>0.02199643552641817</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.207723594510604</v>
+        <v>-0.2127870819490525</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4353613782667267</v>
+        <v>-0.4977454396392744</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7857425155617008</v>
+        <v>-0.8435225576356729</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.3003520457419953</v>
+        <v>-0.3411818020879025</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.0819292216146934</v>
+        <v>-0.1148938454023209</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1857160675942211</v>
+        <v>0.1653279135830559</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3420339855705379</v>
+        <v>0.3292161365840016</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.6591806163006453</v>
+        <v>0.6407108290395698</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.7422492422131199</v>
+        <v>0.7399300161138314</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.488857610395776</v>
+        <v>0.4985289668568171</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.6154693470104178</v>
+        <v>0.607997699068008</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4958812562297652</v>
+        <v>0.5286259018462047</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 37.72</t>
+          <t>X &gt; 37.73</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3299</v>
+        <v>3305</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.04403105141302888</v>
+        <v>0.04198723883999378</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.08212655153793236</v>
+        <v>0.07589537998737939</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.03657581086009287</v>
+        <v>0.0007337544076406743</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3009582921256282</v>
+        <v>-0.3668163758853069</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8228822109274674</v>
+        <v>-0.8560655168372264</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1457165229922666</v>
+        <v>-0.2205230451766909</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.02841948168133968</v>
+        <v>-0.03934116584110114</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.03247529053980003</v>
+        <v>-0.02149798910231482</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2004054766001815</v>
+        <v>0.1531376242518263</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5629753131893978</v>
+        <v>0.5384988862421665</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.7826451764508775</v>
+        <v>0.7878046297580639</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.5745256022223799</v>
+        <v>0.5910432877749514</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.8212434970144571</v>
+        <v>0.8482440767334438</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.5316714782503951</v>
+        <v>0.600269353947688</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 40.2</t>
+          <t>X &gt; 40.21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3140</v>
+        <v>3146</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2827434357934777</v>
+        <v>0.2817663477018542</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.3406910127221181</v>
+        <v>0.3338770690114359</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2175130142151147</v>
+        <v>0.1796397683091229</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.04716721552130565</v>
+        <v>-0.02243342557728312</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5056249407613151</v>
+        <v>-0.5434386795809658</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.09540461320628424</v>
+        <v>0.0151518567038309</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5055042375497365</v>
+        <v>0.4308374632547967</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.342538675101757</v>
+        <v>0.2825658333890857</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.5221590286319682</v>
+        <v>0.4678860156146172</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.8505841813467043</v>
+        <v>0.8190336177148438</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.059895761940005</v>
+        <v>1.059478752903431</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.9031911117475602</v>
+        <v>0.9134601394802928</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.183677201109312</v>
+        <v>1.203723353802545</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.059094379998271</v>
+        <v>1.121460444524011</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 42.68</t>
+          <t>X &gt; 42.69</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2973</v>
+        <v>2979</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.18302941530456</v>
+        <v>-0.1818036171817994</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.03541465492530449</v>
+        <v>0.02869500416628057</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.06163270178440428</v>
+        <v>0.02185677579599599</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.02488207866680625</v>
+        <v>-0.09825620389001699</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6456937122844693</v>
+        <v>-0.6881089665723081</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3300907699458904</v>
+        <v>-0.41532344775338</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2420955004075296</v>
+        <v>0.1611767339802412</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.1056307191196666</v>
+        <v>-0.1705178640959204</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1546261799149562</v>
+        <v>0.09432039195842634</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5828775820378453</v>
+        <v>0.5448043530616218</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.7145370023178472</v>
+        <v>0.709543851870265</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.6480069811111164</v>
+        <v>0.6526064566683161</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.9678494005861253</v>
+        <v>0.9811933209386154</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.126312935104622</v>
+        <v>1.182397706779589</v>
       </c>
     </row>
     <row r="17">
@@ -2786,49 +2786,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2778</v>
+        <v>2784</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.004246970950717355</v>
+        <v>-0.01817923255998721</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.5578081097949905</v>
+        <v>0.5336838302727998</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7214598249801156</v>
+        <v>0.6618787349399113</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8715226736828541</v>
+        <v>0.7917627761545916</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2093036349791291</v>
+        <v>0.1589901332292172</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.5264922067044182</v>
+        <v>0.4317756520481453</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.181035105026353</v>
+        <v>1.088737072689923</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.021941743482337</v>
+        <v>0.9458321917468453</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.161165232976387</v>
+        <v>1.088263960076866</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.643139885170655</v>
+        <v>1.592027772516282</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.762412808983889</v>
+        <v>1.746696079913804</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1.832788081569596</v>
+        <v>1.825649512557334</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.096582512633439</v>
+        <v>2.097612778001256</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.998344080786538</v>
+        <v>2.044430499547353</v>
       </c>
     </row>
     <row r="18">
@@ -2838,101 +2838,101 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2562</v>
+        <v>2565</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.6732895769422811</v>
+        <v>0.6440937825896498</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.147477151820603</v>
+        <v>1.124779625782715</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.9301179179912893</v>
+        <v>0.8868048773433941</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.003975416911551</v>
+        <v>0.9388072986203824</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.6042820509382025</v>
+        <v>0.5663805875749972</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.6111758698705145</v>
+        <v>0.5276396266431505</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.423851386530998</v>
+        <v>1.32368135673233</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.603194189127557</v>
+        <v>1.519842365819393</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.81543607632063</v>
+        <v>1.755455426464529</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.292605492324881</v>
+        <v>2.255614384590352</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.165968346554934</v>
+        <v>2.16829636696081</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.122282486420012</v>
+        <v>2.132319486613717</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>2.248579720538302</v>
+        <v>2.305454307405945</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>2.27915533953923</v>
+        <v>2.382494289289916</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 50.11</t>
+          <t>X &gt; 50.12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2344</v>
+        <v>2347</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.45692986133453</v>
+        <v>1.427734066981898</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.487114230745938</v>
+        <v>1.46226664551272</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.286454143968896</v>
+        <v>1.23881388495451</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.629717208307149</v>
+        <v>1.581554460864794</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.243169499019238</v>
+        <v>1.220019240730252</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.393907327126342</v>
+        <v>1.322519531792686</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2.076787586197064</v>
+        <v>2.028146967471443</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.97523048756122</v>
+        <v>1.902884662601082</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.212883143325136</v>
+        <v>2.16391120203815</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.600165712182985</v>
+        <v>2.574650522457731</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.438126669963744</v>
+        <v>2.45565268879988</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.643153286482892</v>
+        <v>2.684104653921274</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.606961477538078</v>
+        <v>2.654700975604008</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.875359243805576</v>
+        <v>2.971558674914299</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.426430717242908</v>
+        <v>1.397234922890277</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.228122595502938</v>
+        <v>2.200581001047475</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.234437967056621</v>
+        <v>2.181199587370116</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.645693555609853</v>
+        <v>2.591851059562799</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.134115502945441</v>
+        <v>2.10260191861088</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.551990729683581</v>
+        <v>2.468976581089137</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.358044552320841</v>
+        <v>3.297417356627378</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.500446138257495</v>
+        <v>3.439914030029712</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.251934680281359</v>
+        <v>3.215763133574235</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.620956343398298</v>
+        <v>3.608593420330621</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.46313751050144</v>
+        <v>3.49804211645386</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.403751012130087</v>
+        <v>3.462619710159423</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.358658761723383</v>
+        <v>3.423065477387347</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.584394411949916</v>
+        <v>3.700178298949766</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.069265976745939</v>
+        <v>2.040070182393308</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.162188048008687</v>
+        <v>3.161001261564031</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.975424983586457</v>
+        <v>2.975271593582136</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.469664687757245</v>
+        <v>3.469170195379242</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.54522857537566</v>
+        <v>2.563904413761698</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>2.872503784861465</v>
+        <v>2.836689932580626</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.776861619244443</v>
+        <v>3.764073364936024</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.090636286233341</v>
+        <v>4.078271805800725</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.977597908992188</v>
+        <v>3.98929711658073</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.168803527029837</v>
+        <v>4.205510137429812</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.120271030924776</v>
+        <v>4.157375930143338</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.946424300406605</v>
+        <v>4.007534347175415</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.150948095713701</v>
+        <v>4.236401381610023</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.376683745940234</v>
+        <v>4.48544624362539</v>
       </c>
     </row>
     <row r="22">
@@ -3046,725 +3046,725 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.5953303037765</v>
+        <v>1.566134509423868</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.209950662325568</v>
+        <v>3.208763875880912</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.343038515107189</v>
+        <v>3.342885125102868</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.883820843446287</v>
+        <v>3.883326351068284</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.321024523454</v>
+        <v>3.335426183723399</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.358983381298906</v>
+        <v>3.314956570577515</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.624830861140197</v>
+        <v>4.603274088390187</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4.74496127783496</v>
+        <v>4.723951591936462</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4.449099497119576</v>
+        <v>4.452374877227818</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>4.891018633849029</v>
+        <v>4.918868877057989</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>4.745037381636983</v>
+        <v>4.773379455914863</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>4.603255815847852</v>
+        <v>4.655593114100874</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.594144304871506</v>
+        <v>4.670992372287778</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>5.054759579290632</v>
+        <v>5.154641339874999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 60.03</t>
+          <t>X &gt; 60.02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.462680518901614</v>
+        <v>2.433484724548983</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.57213145304415</v>
+        <v>3.570944666599495</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.774573074261241</v>
+        <v>3.77441968425692</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.03751221917674</v>
+        <v>4.037017726798737</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.936403383600272</v>
+        <v>3.945910589828252</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.636167851482377</v>
+        <v>3.621483102675043</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4.81307767813918</v>
+        <v>4.821610026057407</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.342024970607419</v>
+        <v>5.351132275627627</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.148240689250649</v>
+        <v>5.181445665163679</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>5.825546328511756</v>
+        <v>5.88382809961081</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>5.156037733332575</v>
+        <v>5.215188647429727</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.256816948104891</v>
+        <v>5.339712385458192</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.367874594127471</v>
+        <v>5.475410464202923</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>5.593610244354004</v>
+        <v>5.72445532621829</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 62.51</t>
+          <t>X &gt; 62.5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.41923525539606</v>
+        <v>3.489888175113023</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.606838874888957</v>
+        <v>4.548220523919433</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.212067490133919</v>
+        <v>4.305425931831138</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.964077807701109</v>
+        <v>4.05795148247978</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.879646045830818</v>
+        <v>4.021532530207104</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4.025734145057434</v>
+        <v>4.067902954686417</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.924382333446346</v>
+        <v>5.063850639045853</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.818887063335843</v>
+        <v>5.881036746587043</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.682261941608829</v>
+        <v>5.844064137450246</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>6.19391651895522</v>
+        <v>6.378726122672994</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.384071639061148</v>
+        <v>5.57081209023125</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.947950547846119</v>
+        <v>6.157280714388591</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>5.754728590145419</v>
+        <v>5.988537882164394</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.05610720557619</v>
+        <v>6.313054442292966</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 64.99</t>
+          <t>X &gt; 64.98</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1141</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>3.960801760876684</v>
+        <v>3.931605966524053</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.540676141081924</v>
+        <v>4.539489354637269</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.671759269911455</v>
+        <v>4.671605879907133</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.539057156707536</v>
+        <v>4.538562664329532</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>4.52662211719641</v>
+        <v>4.575168036962182</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.122856795385395</v>
+        <v>4.146814204335008</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4.739285787565329</v>
+        <v>4.78729746655565</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>6.025065522393845</v>
+        <v>6.074313084787562</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>6.139368203732595</v>
+        <v>6.212625313512291</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>6.691728110294939</v>
+        <v>6.791075435589512</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.785887600588644</v>
+        <v>5.88579563660732</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>6.609047523320825</v>
+        <v>6.73274414434907</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>6.627108764661223</v>
+        <v>6.775798312439051</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>6.765201995957</v>
+        <v>6.937200755523662</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 67.46</t>
+          <t>X &gt; 67.45</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>977</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.711509762710271</v>
+        <v>3.68231396835764</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.761531448561485</v>
+        <v>4.760344662116829</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.287947371892429</v>
+        <v>5.287793981888107</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.827589096852336</v>
+        <v>5.827094604474333</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.391653689099527</v>
+        <v>5.440199608865299</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.279611137363069</v>
+        <v>5.303568546312682</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>6.013733940839998</v>
+        <v>6.061745619830319</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>6.979623331853659</v>
+        <v>7.028870894247376</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>7.225703611359542</v>
+        <v>7.298960721139238</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>7.70638870448721</v>
+        <v>7.805736029781784</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>6.8875626741697</v>
+        <v>6.987470710188376</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.945482279953886</v>
+        <v>8.069178900982131</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>8.241810444040681</v>
+        <v>8.390499991818508</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.853421222209896</v>
+        <v>8.025419981776558</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 69.94</t>
+          <t>X &gt; 69.93</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>844</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.746572121124416</v>
+        <v>4.717376326771785</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.623537686828357</v>
+        <v>5.622350900383701</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.532083837618352</v>
+        <v>6.53193044761403</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7.136242630495808</v>
+        <v>7.135748138117805</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.427336963656039</v>
+        <v>7.475882883421811</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.013810519357477</v>
+        <v>7.03776792830709</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.758484046347228</v>
+        <v>7.806495725337548</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.187149999716887</v>
+        <v>9.236397562110604</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.770717606227279</v>
+        <v>8.843974716006976</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>8.631699283831068</v>
+        <v>8.731046609125642</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.308514713248613</v>
+        <v>8.408422749267288</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>9.527726988826679</v>
+        <v>9.651423609854923</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>9.699993197124641</v>
+        <v>9.848682744902469</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>8.859378136450708</v>
+        <v>9.03137689601737</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 72.42</t>
+          <t>X &gt; 72.41</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>711</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.746932070731468</v>
+        <v>5.717736276378837</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.682862714657794</v>
+        <v>5.681675928213139</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.131973186442835</v>
+        <v>6.131819796438513</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.387374138751312</v>
+        <v>7.386879646373309</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7.271025513925665</v>
+        <v>7.319571433691436</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>6.161929782660614</v>
+        <v>6.185887191610227</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>7.483689184294583</v>
+        <v>7.531700863284904</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.563737277497999</v>
+        <v>8.612984839891716</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>8.502755120975223</v>
+        <v>8.57601223075492</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.637365157275468</v>
+        <v>8.736712482570042</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>8.292017022925251</v>
+        <v>8.391925058943926</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>9.5922179600907</v>
+        <v>9.715914581118945</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>9.594008035047338</v>
+        <v>9.742697582825166</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>9.538449733093849</v>
+        <v>9.710448492660511</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 74.9</t>
+          <t>X &gt; 74.89</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>5.413820811570915</v>
+        <v>5.453763380367526</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5.282897876401819</v>
+        <v>5.184215195047479</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.71049491269941</v>
+        <v>5.611495269130145</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6.334141108919354</v>
+        <v>6.398193760262728</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.453746292665762</v>
+        <v>6.401555456749229</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>6.093225585458747</v>
+        <v>6.017526525650261</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.324304699876784</v>
+        <v>7.270499336260592</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.66644658240584</v>
+        <v>8.610906313151467</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8.605464425883063</v>
+        <v>8.573933704014671</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.084492997974252</v>
+        <v>8.07851234815864</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.044265523924579</v>
+        <v>8.038575513102018</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.901012097332547</v>
+        <v>9.081963925343764</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>9.632177033492809</v>
+        <v>9.836231286136261</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>9.693438999508821</v>
+        <v>9.921072535672145</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 77.38</t>
+          <t>X &gt; 77.36</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>6.628395710356337</v>
+        <v>6.479787165012006</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.422067916887642</v>
+        <v>5.502670685916755</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>6.241871430918032</v>
+        <v>6.321053909723268</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.19395892268453</v>
+        <v>8.269119769119769</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>6.441094470803414</v>
+        <v>6.365729214026423</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>6.738468500438501</v>
+        <v>6.638514732845351</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.463474740362621</v>
+        <v>7.385939451700708</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>9.425555894146733</v>
+        <v>9.546369317579995</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>9.971861187016671</v>
+        <v>9.913437112483599</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.324371540484378</v>
+        <v>9.29162873368881</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.714812082629038</v>
+        <v>8.885468084132526</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10.5710525831625</v>
+        <v>10.76181663967923</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>11.36547662863451</v>
+        <v>11.57877992523662</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>11.59121227886104</v>
+        <v>11.82782478725199</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 79.86</t>
+          <t>X &gt; 79.84</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.883425054736968</v>
+        <v>4.706383020473837</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.305830692939288</v>
+        <v>4.411865729132423</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>6.236640703533091</v>
+        <v>6.337715369683693</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.400457578387602</v>
+        <v>7.498527245949923</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>5.31178042839268</v>
+        <v>5.462886352420682</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>5.350756525211231</v>
+        <v>5.477939912476721</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>7.074831695660826</v>
+        <v>7.221407534591471</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.450140312856</v>
+        <v>9.590626320599888</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>9.647556089149759</v>
+        <v>9.811385670225967</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>9.056035225636435</v>
+        <v>9.245289048173873</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>8.076140268926636</v>
+        <v>8.267952724349129</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>10.64570709058</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>11.82473449303313</v>
+        <v>12.05467287535638</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.75848047917699</v>
+        <v>11.01505794355732</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 82.33</t>
+          <t>X &gt; 82.32</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>290</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.415635693603583</v>
+        <v>4.386439899250952</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>3.494104772953548</v>
+        <v>3.492917986508893</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.582092008888161</v>
+        <v>7.581938618883839</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>10.47093784213168</v>
+        <v>10.47044334975368</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.898165530415312</v>
+        <v>8.946711450181084</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.161056801429709</v>
+        <v>8.185014210379322</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.766001614577334</v>
+        <v>8.814013293567655</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>10.71272607423887</v>
+        <v>10.76197363663258</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>13.75519219357817</v>
+        <v>13.82844930335786</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>13.2501009834552</v>
+        <v>13.34944830874977</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>12.35574465278121</v>
+        <v>12.45565268879989</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>14.80391590858481</v>
+        <v>14.92761252961305</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>16.10790298630589</v>
+        <v>16.25659253408372</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>15.29915587791172</v>
+        <v>15.47115463747839</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 84.81</t>
+          <t>X &gt; 84.79</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>189</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.545538995920673</v>
+        <v>2.516343201568041</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.167157135661071</v>
+        <v>5.165970349216416</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>8.476089454609742</v>
+        <v>8.47593606460542</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.19361618549969</v>
+        <v>10.19312169312168</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.068025045102409</v>
+        <v>8.116570964868181</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.894499603838021</v>
+        <v>8.918457012787634</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>13.10462536268988</v>
+        <v>13.1538729250836</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>16.7473469098708</v>
+        <v>16.8206040196505</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>16.955629171742</v>
+        <v>17.05497649703658</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>16.75092801348181</v>
+        <v>16.85083604950049</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>18.37260775313873</v>
+        <v>18.49630437416698</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>20.59795954532795</v>
+        <v>20.74664909310578</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>18.70729307915237</v>
+        <v>18.87929183871903</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 87.29</t>
+          <t>X &gt; 87.27</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>127</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.574202079701863</v>
+        <v>6.545006285349231</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.963015986638034</v>
+        <v>4.961829200193378</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>7.717850901095602</v>
+        <v>7.717697511091281</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.635477619487112</v>
+        <v>8.634983127109109</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>8.097188066391418</v>
+        <v>8.14573398615719</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>9.181963670829653</v>
+        <v>9.205921079779266</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.45945803597294</v>
+        <v>11.50746971496326</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>14.1419956913988</v>
+        <v>14.19124325379251</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>15.65581668448232</v>
+        <v>15.72907379426201</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>15.5932994629556</v>
+        <v>15.69264678825017</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.96340145430172</v>
+        <v>17.06330949032039</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>21.72218905547593</v>
+        <v>21.84588567650417</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>22.08943977696568</v>
+        <v>22.2381293247435</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>20.7403722775859</v>
+        <v>20.91237103715256</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 89.77</t>
+          <t>X &gt; 89.75</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>5.852417302798983</v>
+        <v>5.823221508446352</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>1.860278828782775</v>
+        <v>1.859092042338119</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.846459824980116</v>
+        <v>3.846306434975794</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>3.976190476190474</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>5.819347796425156</v>
+        <v>5.867893716190927</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>6.116721826060243</v>
+        <v>6.140679235009856</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>15.08875234681685</v>
+        <v>15.13799990921057</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>17.40872257124647</v>
+        <v>17.48197968102617</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>18.93975615586899</v>
+        <v>19.03910348116356</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>18.7350549976088</v>
+        <v>18.83496303362747</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>24.72181410234507</v>
+        <v>24.84551072337332</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>26.68261562998406</v>
+        <v>26.83130517776188</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>23.33692270878202</v>
+        <v>23.50892146834868</v>
       </c>
     </row>
   </sheetData>
@@ -3904,573 +3904,573 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 17.89</t>
+          <t>X &lt; 17.92</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5.431707400211344</v>
+        <v>5.430520613766689</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5.036936015456305</v>
+        <v>5.036782625451984</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>8.738589730473237</v>
+        <v>8.738095238095234</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.390776367853739</v>
+        <v>9.439322287619511</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4.92624563558406</v>
+        <v>4.950203044533673</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.651059085841702</v>
+        <v>3.699070764832022</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.8030380611025834</v>
+        <v>0.8522856234963001</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.829372666848762</v>
+        <v>-2.756115557069066</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-7.250720034607198</v>
+        <v>-7.151372709312625</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-7.455421192867391</v>
+        <v>-7.355513156848716</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-7.421043040512068</v>
+        <v>-7.297346419483823</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.502028155571459</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-7.615458243598944</v>
+        <v>-8.633935674508479</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 20.37</t>
+          <t>X &lt; 20.39</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4.319083969465645</v>
+        <v>3.839094524319364</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>7.50789787640182</v>
+        <v>7.017822201068277</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.113126491646781</v>
+        <v>6.624084212753573</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8.843351635235145</v>
+        <v>9.134920634920626</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>8.30506208213945</v>
+        <v>8.645671493968706</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3.802436111774533</v>
+        <v>4.156552250882882</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.5177257525083689</v>
+        <v>0.9212929870542439</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.7493428912783671</v>
+        <v>-0.3381905669798897</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.610325047801147</v>
+        <v>-1.962464763418275</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-5.66024384413101</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-7.464945002391204</v>
+        <v>-7.752338553674115</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-8.230566850035878</v>
+        <v>-7.694171816309222</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-9.450717703349291</v>
+        <v>-8.882980536523846</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-10.82498205312275</v>
+        <v>-11.01488805546085</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 22.85</t>
+          <t>X &lt; 22.87</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>178</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.384252508791484</v>
+        <v>5.590446834330898</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.020257426963617</v>
+        <v>6.241906620683423</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6.749081547826563</v>
+        <v>6.965487068122904</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.126497702650873</v>
+        <v>9.330007980845963</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7.464612643937194</v>
+        <v>7.723440404139858</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4.952997909527348</v>
+        <v>4.976955318476961</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>3.182894291834202</v>
+        <v>3.230905970824523</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>3.277623400856456</v>
+        <v>3.326870963250173</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.531247985906724</v>
+        <v>1.60450509568642</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.12765957446809</v>
+        <v>-2.028312249173517</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-4.017753991155239</v>
+        <v>-3.917845955136563</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-3.983375838799915</v>
+        <v>-3.859679217771671</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.403526692113324</v>
+        <v>-4.254837144335497</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-5.301386547504777</v>
+        <v>-5.691185540747099</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 25.33</t>
+          <t>X &lt; 25.35</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.475605708596085</v>
+        <v>4.571433239490695</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>6.777463093793131</v>
+        <v>6.421732549184632</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.687039535125038</v>
+        <v>8.173917307651045</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.252047287409063</v>
+        <v>8.732985898221941</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.713757734313369</v>
+        <v>8.243736757270021</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.53287089438323</v>
+        <v>4.909152141413806</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.274247491638803</v>
+        <v>2.508594574355826</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.241961456547713</v>
+        <v>2.29120901894143</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.746196691329288</v>
+        <v>1.819453801108985</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.147200365870141</v>
+        <v>-2.047853040575568</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.786684132825982</v>
+        <v>-2.686776096807307</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.621871197861971</v>
+        <v>-3.498174576833726</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.938927310336183</v>
+        <v>-3.02376728600624</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.793403105754336</v>
+        <v>-4.513852858773483</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 27.81</t>
+          <t>X &lt; 27.82</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5.413820811570915</v>
+        <v>5.282095967320814</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.434213665875504</v>
+        <v>5.971646154892227</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>8.342073860067828</v>
+        <v>8.499986088655447</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>8.143351635235142</v>
+        <v>8.305194805194802</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6.947167345297345</v>
+        <v>7.166595014892231</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4.941909795985069</v>
+        <v>5.035514041896789</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.554567857771517</v>
+        <v>2.555279915158813</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.41644658240584</v>
+        <v>2.27695385144321</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.368622320619899</v>
+        <v>1.256374684929362</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7970859493941589</v>
+        <v>-0.8789293057216767</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.646523949759619</v>
+        <v>-2.72241401555285</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-3.095253318682744</v>
+        <v>-3.319984983105996</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.346081941759884</v>
+        <v>-2.731536352292771</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.936609960099503</v>
+        <v>-3.466098047654455</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 30.29</t>
+          <t>X &lt; 30.3</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.4736294240111008</v>
+        <v>0.6430413282661718</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>3.407897876401812</v>
+        <v>3.339143522389598</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5.28585376437406</v>
+        <v>5.648108236777588</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>5.643351635235142</v>
+        <v>6.003217503217506</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.332334809412174</v>
+        <v>5.73919358749081</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.129708839047261</v>
+        <v>3.439937538782843</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.454089388872006</v>
+        <v>1.700579060457962</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.6038883458238331</v>
+        <v>-0.4515692517871557</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.4375977750738755</v>
+        <v>-0.2617844913094345</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-3.105698389585555</v>
+        <v>-3.126429398655027</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.083126820573014</v>
+        <v>-2.877055106962096</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.610976872814916</v>
+        <v>-3.499160478440743</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.910991675952026</v>
+        <v>-3.894318405004569</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.564570153809257</v>
+        <v>-3.872030912603705</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 32.77</t>
+          <t>X &lt; 32.78</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.5946551469700339</v>
+        <v>0.6257766768551747</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.971166769196188</v>
+        <v>1.830056037692351</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.158117704300551</v>
+        <v>3.178478328123298</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.815583621175392</v>
+        <v>4.179442508710792</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.804534841366156</v>
+        <v>4.212841451382573</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.289958080140082</v>
+        <v>1.621855998909133</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.6780069475874555</v>
+        <v>0.96014302590428</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.8435432427722276</v>
+        <v>-0.6342459418443767</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.431766172581462</v>
+        <v>-1.277418815214432</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-3.160419591055444</v>
+        <v>-2.978440378485558</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-3.448043593940497</v>
+        <v>-3.358019422512882</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.438679724815415</v>
+        <v>-2.422659702691845</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.823862579674376</v>
+        <v>-3.870449208203041</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.681619221264349</v>
+        <v>-3.972281539170133</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 35.24</t>
+          <t>X &lt; 35.26</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.1127439118287583</v>
+        <v>0.2716285460117263</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.6629411040675208</v>
+        <v>0.5429450414550203</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.420907471473875</v>
+        <v>1.433087224324346</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.703870367223615</v>
+        <v>2.989504789076825</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.471056318450685</v>
+        <v>4.725036573333796</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.174770405722654</v>
+        <v>2.364877068649761</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.225506732335461</v>
+        <v>1.382929408576047</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2502074445924976</v>
+        <v>-0.1503105369190934</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.8875584771959666</v>
+        <v>-0.8267231104352462</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.457938368626692</v>
+        <v>-2.368942495847925</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.873891611337811</v>
+        <v>-2.8604392652231</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.606289393388479</v>
+        <v>-1.652847240501885</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.236824794521496</v>
+        <v>-2.191683327985253</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.787300893702458</v>
+        <v>-1.942638465969885</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 37.72</t>
+          <t>X &lt; 37.73</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1272994978133397</v>
+        <v>-0.1183122804678476</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.2132939728426919</v>
+        <v>0.2347293131917851</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1629542758029245</v>
+        <v>0.2965721904807239</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.556095607680611</v>
+        <v>1.793198828506348</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.543638431163558</v>
+        <v>3.648476873056872</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.085558959076479</v>
+        <v>1.362466580084885</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.5416063495232919</v>
+        <v>0.7943088600701174</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4189693934518175</v>
+        <v>0.6207284697423532</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.101255013357985</v>
+        <v>0.074845005850257</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.462542694705718</v>
+        <v>-1.373740555533686</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.294864450032165</v>
+        <v>-2.318883120218679</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.507064545888412</v>
+        <v>-1.57185300742325</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.440798441526908</v>
+        <v>-2.541063746845857</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.459624085455317</v>
+        <v>-1.717966071971709</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 40.2</t>
+          <t>X &lt; 40.21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1025</v>
+        <v>1030</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.8304305936411538</v>
+        <v>-0.8225515548773359</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.596956492530218</v>
+        <v>-0.5735203468798673</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4092036054406023</v>
+        <v>-0.2922342271907183</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.206458431351642</v>
+        <v>0.4162419065986995</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.901178586993815</v>
+        <v>2.006889855187076</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.1597176651726002</v>
+        <v>0.4022389313521657</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.9929538591421192</v>
+        <v>-0.7657906149229774</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5862360951618726</v>
+        <v>-0.4050324053609344</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.035567766247752</v>
+        <v>-0.8735020465485874</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.027202055987175</v>
+        <v>-1.935678284112868</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.665723212507935</v>
+        <v>-2.669891335304563</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.189671036988173</v>
+        <v>-2.223375083376567</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.044479886585151</v>
+        <v>-3.103969903144275</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.766445467756895</v>
+        <v>-2.95201241976968</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 42.68</t>
+          <t>X &lt; 42.69</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.4848316720554493</v>
+        <v>0.4799213977043735</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.2938627886825245</v>
+        <v>0.3087044454388916</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.0661757815381776</v>
+        <v>0.164135892340127</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3634853027372316</v>
+        <v>0.5431893687707543</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.913750469775202</v>
+        <v>2.011463363501228</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.20861823374613</v>
+        <v>1.41641015965925</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1292249576002362</v>
+        <v>0.07015042067437349</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6568392306932225</v>
+        <v>0.8165713377820154</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.09460394133836303</v>
+        <v>0.2424149643972342</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.9599093959704703</v>
+        <v>-0.8690768193372662</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.285865504483255</v>
+        <v>-1.277818921259744</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.121689128092825</v>
+        <v>-1.136109995089505</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.914757938051714</v>
+        <v>-1.948978865680061</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.398136415538858</v>
+        <v>-2.535355891718162</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1387</v>
+        <v>1392</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.03345178555760242</v>
+        <v>0.06131674654158559</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.7875044224487553</v>
+        <v>-0.7361460528999757</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.254114887663562</v>
+        <v>-1.12988404121468</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.483085146374052</v>
+        <v>-1.319258654140725</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.1535586075157269</v>
+        <v>-0.05383119695028427</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.7182535433978714</v>
+        <v>-0.5292256632414976</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.952389190020376</v>
+        <v>-1.768933055607327</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.701067029209412</v>
+        <v>-1.551708232110457</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.905727346651723</v>
+        <v>-1.76547539856665</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.861106532844161</v>
+        <v>-2.766352369518408</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.099477376491926</v>
+        <v>-3.075956506602417</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.242805870914211</v>
+        <v>-3.233307010616826</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.768873322945836</v>
+        <v>-3.772143098100202</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.64920699904922</v>
+        <v>-3.738615477464137</v>
       </c>
     </row>
     <row r="18">
@@ -4532,101 +4532,101 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1603</v>
+        <v>1611</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.052344601962929</v>
+        <v>-0.9986991166821753</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.545518272666513</v>
+        <v>-1.500696317450249</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.319171644999187</v>
+        <v>-1.244284464756554</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.375281905137527</v>
+        <v>-1.266907999293664</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.7334472346307379</v>
+        <v>-0.671994966554891</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.6845204099645983</v>
+        <v>-0.551329251553085</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.916581270487285</v>
+        <v>-1.755005602557034</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.259349106318773</v>
+        <v>-2.126117633717371</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.536195694567311</v>
+        <v>-2.440229748312838</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.291108809905744</v>
+        <v>-3.231367982856284</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.089353470635281</v>
+        <v>-3.092411268048501</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.021844108602856</v>
+        <v>-3.034244530683608</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.221790022551289</v>
+        <v>-3.305255964385857</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.33702197826311</v>
+        <v>-3.490723827386013</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 50.11</t>
+          <t>X &lt; 50.12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1821</v>
+        <v>1829</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.852157145897934</v>
+        <v>-1.803590085756547</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.659078613483366</v>
+        <v>-1.619118165072742</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.507103142032832</v>
+        <v>-1.440236909238941</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.894941581395059</v>
+        <v>-1.825841822847821</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.393843825956829</v>
+        <v>-1.36055321813835</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.534106557809714</v>
+        <v>-1.440091492899832</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.356056404032415</v>
+        <v>-2.289660605578739</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.275779672887566</v>
+        <v>-2.181382835704078</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.526863930605089</v>
+        <v>-2.46239544893848</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.019147953720051</v>
+        <v>-2.984380953571552</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.810997633970153</v>
+        <v>-2.83170363303919</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.076425325077011</v>
+        <v>-3.127099862687245</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.028324728596267</v>
+        <v>-3.084860304286607</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.432120987774049</v>
+        <v>-3.546586355338491</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2032</v>
+        <v>2041</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.47650642739864</v>
+        <v>-1.437987068551706</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.10778071252517</v>
+        <v>-2.069885692100371</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.208578554899034</v>
+        <v>-2.145563483723393</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.591942482411909</v>
+        <v>-2.526981802970099</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.051800662958591</v>
+        <v>-2.014360748094781</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-2.44070114312742</v>
+        <v>-2.350841457292468</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-3.235486606491143</v>
+        <v>-3.167986908677264</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-3.431972920719005</v>
+        <v>-3.364154008591257</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-3.123923476863489</v>
+        <v>-3.082273417473509</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-3.506216339219414</v>
+        <v>-3.489041403809516</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-3.341112078558275</v>
+        <v>-3.373655967351958</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.280714342661248</v>
+        <v>-3.338619371584805</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.232124491347321</v>
+        <v>-3.292816984576852</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.521438746036146</v>
+        <v>-3.631719207323847</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2244</v>
+        <v>2253</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.749208713461179</v>
+        <v>-1.71576054509881</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.494941520226398</v>
+        <v>-2.481809881345264</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-2.42295872806028</v>
+        <v>-2.411055166908774</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.802474297269299</v>
+        <v>-2.788428760810561</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.008614649654518</v>
+        <v>-2.017037444602302</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-2.244100300303622</v>
+        <v>-2.207396837524414</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.971923292360579</v>
+        <v>-2.952846639297768</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.282676224611699</v>
+        <v>-3.262999268681028</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.142739454203998</v>
+        <v>-3.144153854761932</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-3.302236726693287</v>
+        <v>-3.324653718659214</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.260939661937257</v>
+        <v>-3.283831292613655</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.113915024568378</v>
+        <v>-3.157868011712729</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-3.287688750119891</v>
+        <v>-3.352072521143775</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-3.528368862391922</v>
+        <v>-3.612060080062975</v>
       </c>
     </row>
     <row r="22">
@@ -4740,725 +4740,725 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2462</v>
+        <v>2471</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.08584930995206</v>
+        <v>-1.060836462568147</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-2.028995327481674</v>
+        <v>-2.019185003478199</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-2.200349833727557</v>
+        <v>-2.190491845980425</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.534786016586722</v>
+        <v>-2.523204928888127</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-2.141901480613591</v>
+        <v>-2.14477909486898</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-2.1279282606951</v>
+        <v>-2.092767431272627</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.960929573534564</v>
+        <v>-2.939347314264026</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.082892324017436</v>
+        <v>-3.061338768529389</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.839023872284322</v>
+        <v>-2.834967776470563</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.140535814933934</v>
+        <v>-3.152815710755632</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-3.039792872573756</v>
+        <v>-3.052668332581099</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.943229187698215</v>
+        <v>-2.973024697264812</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.935735973751235</v>
+        <v>-2.982610679843297</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.297443466607724</v>
+        <v>-3.359417935401503</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 60.03</t>
+          <t>X &lt; 60.02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2659</v>
+        <v>2669</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.37646077033218</v>
+        <v>-1.354257984469385</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.844911112362219</v>
+        <v>-1.836668246111472</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.032770848180867</v>
+        <v>-2.024340331193365</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.145254061916276</v>
+        <v>-2.136164880285818</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-2.083843465086943</v>
+        <v>-2.083135836780372</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.879153689500299</v>
+        <v>-1.865350969376713</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.506730361520134</v>
+        <v>-2.504217725451987</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.841650583586059</v>
+        <v>-2.838413085893997</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2.695310032786139</v>
+        <v>-2.70625267998107</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-3.074888981194469</v>
+        <v>-3.09894365688357</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-2.696199698108707</v>
+        <v>-2.721923193917441</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.754430059355684</v>
+        <v>-2.793504448401116</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.816131237183875</v>
+        <v>-2.869069354073325</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.983838766172774</v>
+        <v>-3.049536309666991</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 62.51</t>
+          <t>X &lt; 62.5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2843</v>
+        <v>2851</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-1.570551884876089</v>
+        <v>-1.602290595836706</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.973012806610441</v>
+        <v>-1.945192507667706</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.858982828605498</v>
+        <v>-1.901422425960611</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.710311175840914</v>
+        <v>-1.753158236380891</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.669131466247656</v>
+        <v>-1.73450388620666</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.70384238699782</v>
+        <v>-1.72295939987746</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.085783019421456</v>
+        <v>-2.150007844918392</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.534390276325759</v>
+        <v>-2.562468447540589</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.436448643306768</v>
+        <v>-2.511017517853382</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.670711002543371</v>
+        <v>-2.755992841078118</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.294460111316013</v>
+        <v>-2.380874387535798</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.557456129473486</v>
+        <v>-2.654364095113479</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.466470164671364</v>
+        <v>-2.574959431868791</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-2.64376502885262</v>
+        <v>-2.762979786014874</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 64.99</t>
+          <t>X &lt; 64.98</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3024</v>
+        <v>3035</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.476635490527769</v>
+        <v>-1.460243058482781</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.555870239540212</v>
+        <v>-1.549803514571877</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-1.669740065190119</v>
+        <v>-1.663651980432391</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.588026083947454</v>
+        <v>-1.582101806239748</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.581386978196853</v>
+        <v>-1.594092392312923</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.398355444953694</v>
+        <v>-1.402393860149992</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.597483749306214</v>
+        <v>-1.60993646725214</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.113039260915336</v>
+        <v>-2.124100590311819</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.123497712046778</v>
+        <v>-2.14364688538987</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.328407648622424</v>
+        <v>-2.357737584976618</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.986781804505505</v>
+        <v>-2.017571528584504</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.29798258037296</v>
+        <v>-2.336702300130455</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.303610265332757</v>
+        <v>-2.351830527112959</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.390590518731223</v>
+        <v>-2.44738197559893</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 67.46</t>
+          <t>X &lt; 67.45</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3188</v>
+        <v>3199</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-1.121965702511865</v>
+        <v>-1.109115560877029</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.310852123598181</v>
+        <v>-1.305995232060901</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-1.532825368309453</v>
+        <v>-1.527525340725148</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.667467626803628</v>
+        <v>-1.661599074032864</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.532410548451736</v>
+        <v>-1.542152596598527</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-1.468652749301818</v>
+        <v>-1.471018390719571</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.661929959541716</v>
+        <v>-1.67106855727237</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.987163805492528</v>
+        <v>-1.995571147917417</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-2.031496360046681</v>
+        <v>-2.047180297572012</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.175532064682386</v>
+        <v>-2.198798485742458</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.924612818122945</v>
+        <v>-1.948922038202639</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.249375627465341</v>
+        <v>-2.279941144346587</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.339021246779829</v>
+        <v>-2.377028155571459</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.253087448354876</v>
+        <v>-2.298622555825546</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 69.94</t>
+          <t>X &lt; 69.93</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3321</v>
+        <v>3332</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-1.191173978944668</v>
+        <v>-1.179768028175474</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.286821595545383</v>
+        <v>-1.28228412535384</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-1.575709042566899</v>
+        <v>-1.570484870239092</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.699788562903557</v>
+        <v>-1.694066854749089</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.771814794737423</v>
+        <v>-1.778448268672449</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.638717387774882</v>
+        <v>-1.639474742748909</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.797658862876247</v>
+        <v>-1.804073889256031</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.188717703421446</v>
+        <v>-2.19416363325854</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.053379768185998</v>
+        <v>-2.065446721359784</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.015131062176124</v>
+        <v>-2.034038005646991</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.932815038492286</v>
+        <v>-1.952143413149145</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-2.24320603149841</v>
+        <v>-2.267638075438349</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.2858772457936</v>
+        <v>-2.316609613717276</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.103994398801767</v>
+        <v>-2.141338635692946</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 72.42</t>
+          <t>X &lt; 72.41</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3454</v>
+        <v>3465</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.168542220323801</v>
+        <v>-1.158760473535636</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.033821685052303</v>
+        <v>-1.030303577859918</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.182400203879908</v>
+        <v>-1.178626438058345</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.412075616496963</v>
+        <v>-1.407502569373079</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.386419292391302</v>
+        <v>-1.392160564588728</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.131359382159602</v>
+        <v>-1.132777225028804</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.373981846451478</v>
+        <v>-1.379654273570438</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.623331330584733</v>
+        <v>-1.628473317936809</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.582108800330786</v>
+        <v>-1.592399350125206</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-1.606802548584454</v>
+        <v>-1.622470459453332</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.535410724115238</v>
+        <v>-1.551426816430201</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.803483516702542</v>
+        <v>-1.823628233045703</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.802671393653192</v>
+        <v>-1.828052391001357</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.82162362810827</v>
+        <v>-1.851828892401684</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 74.9</t>
+          <t>X &lt; 74.89</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3557</v>
+        <v>3567</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.9122885795539517</v>
+        <v>-0.9179330539372543</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.7718443483109851</v>
+        <v>-0.754367423594104</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.8994295621648831</v>
+        <v>-0.8816607720299814</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.9784594104615181</v>
+        <v>-0.988398098965618</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.9970130720949868</v>
+        <v>-0.9873315954102111</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9089243370333264</v>
+        <v>-0.8952848009541725</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.090803989354711</v>
+        <v>-1.080821046397233</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.34636787022869</v>
+        <v>-1.335751640107716</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.308022970316593</v>
+        <v>-1.301681599835568</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.216098941013911</v>
+        <v>-1.214326930485832</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.208765227110298</v>
+        <v>-1.207053773095211</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-1.355601972261219</v>
+        <v>-1.385659805919936</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-1.479273071533662</v>
+        <v>-1.513238917903301</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.519162542299028</v>
+        <v>-1.557160473258925</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 77.38</t>
+          <t>X &lt; 77.36</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3671</v>
+        <v>3681</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.8793959436722432</v>
+        <v>-0.8587853495215256</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.6030985938669886</v>
+        <v>-0.6137329934438611</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7660695974352407</v>
+        <v>-0.7763010045330532</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.001581806764314</v>
+        <v>-1.011166157061581</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.7645031352518572</v>
+        <v>-0.7542510766855628</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.778591341337723</v>
+        <v>-0.7649862569933887</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.8486690272632487</v>
+        <v>-0.8381671238158503</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.137920536097525</v>
+        <v>-1.153797525792712</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.184209705037276</v>
+        <v>-1.176134677033936</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.094257449573192</v>
+        <v>-1.089797468632902</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.011814898961696</v>
+        <v>-1.034743806763402</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.261876406256953</v>
+        <v>-1.287429555643527</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.367493302477833</v>
+        <v>-1.396107460297159</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.426344079818477</v>
+        <v>-1.458090601352893</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 79.86</t>
+          <t>X &lt; 79.84</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3778</v>
+        <v>3788</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.4893570751136167</v>
+        <v>-0.4711747030769331</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.3190150523580684</v>
+        <v>-0.3301310153059873</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.5676336033650955</v>
+        <v>-0.5781034974625712</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.6607666329802768</v>
+        <v>-0.6709922515609748</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.4455056495743079</v>
+        <v>-0.4613511763934355</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.4242939463342879</v>
+        <v>-0.4376739186857606</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5739519225246639</v>
+        <v>-0.5894667845751016</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.8417318976208676</v>
+        <v>-0.8565528934603037</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.835490260595229</v>
+        <v>-0.8528601869009691</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.7720365464049408</v>
+        <v>-0.7921201475284221</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.6711867373819516</v>
+        <v>-0.6915471220042875</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.9131065325755543</v>
+        <v>-0.935366271223991</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.053998994696208</v>
+        <v>-1.078433539577794</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.972361619030643</v>
+        <v>-0.9995514033765787</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 82.33</t>
+          <t>X &lt; 82.32</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3875</v>
+        <v>3886</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3204222033738588</v>
+        <v>-0.3172418582288685</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1430411511258427</v>
+        <v>-0.1425449387755222</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.4981962052137447</v>
+        <v>-0.496777988940039</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.68869469681119</v>
+        <v>-0.6867116456438893</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.5695002247606524</v>
+        <v>-0.5716808299304645</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4899151630130021</v>
+        <v>-0.4904015486132991</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.5091676014328996</v>
+        <v>-0.5114780835282815</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.6788455967666494</v>
+        <v>-0.6807736433759217</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.8804281405846552</v>
+        <v>-0.883662643752622</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.8398262107203394</v>
+        <v>-0.8452152849032686</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.7724230838764967</v>
+        <v>-0.7780480231994744</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9558699194194276</v>
+        <v>-0.9628373071969278</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.05216249179098</v>
+        <v>-1.060813851480901</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.018530440219529</v>
+        <v>-1.029102696541166</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 84.81</t>
+          <t>X &lt; 84.79</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3976</v>
+        <v>3987</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1119012398600034</v>
+        <v>-0.1101118248869781</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1302164666272745</v>
+        <v>-0.1297980373246617</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.335882788513743</v>
+        <v>-0.3349508603385232</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.3927748073137778</v>
+        <v>-0.3916687515636781</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2901700383122403</v>
+        <v>-0.2918374435402242</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.3053952135266726</v>
+        <v>-0.3057716857839878</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.426688005965147</v>
+        <v>-0.4279531043050255</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5034363116701357</v>
+        <v>-0.5045531300366761</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.651169056844104</v>
+        <v>-0.6531000021497064</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.6582337938797451</v>
+        <v>-0.6614728155039415</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.6479558091265574</v>
+        <v>-0.6512525052196452</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.7252878153450766</v>
+        <v>-0.7295826882706038</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.8297471225094597</v>
+        <v>-0.8350271525624251</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.7660283307887497</v>
+        <v>-0.7726722827710333</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 87.29</t>
+          <t>X &lt; 87.27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4038</v>
+        <v>4049</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1975292124647439</v>
+        <v>-0.1959808549214515</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04271940754879466</v>
+        <v>-0.0425624879793034</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.1771674080815515</v>
+        <v>-0.176682070771335</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1817471789941081</v>
+        <v>-0.1812374617252743</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1630377448929252</v>
+        <v>-0.1642825845905946</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1734412980129107</v>
+        <v>-0.1738036693177563</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.2199751127573961</v>
+        <v>-0.2210475783632404</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.327384434305074</v>
+        <v>-0.3282087690819466</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3500727598961291</v>
+        <v>-0.3516707993929415</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.3452512661992841</v>
+        <v>-0.3477704393891088</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.3876868979616077</v>
+        <v>-0.3901110038848614</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.5374975431051823</v>
+        <v>-0.5403434454973919</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.547721912311907</v>
+        <v>-0.5514108716208383</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.5309751189969489</v>
+        <v>-0.535522192049541</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 89.77</t>
+          <t>X &lt; 89.75</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4081</v>
+        <v>4092</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1115950730355735</v>
+        <v>-0.1105990356056168</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.07354654486016443</v>
+        <v>0.07337775662382739</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.01473274588988005</v>
+        <v>-0.01468958419717126</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.006588007760200298</v>
+        <v>0.006582155046316984</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.02941224548891341</v>
+        <v>-0.03049343676827476</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.01209066738907438</v>
+        <v>-0.01263086951975367</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1079102553194176</v>
+        <v>-0.1087685455688927</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1946083671775583</v>
+        <v>-0.1952637037016416</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2176671917071644</v>
+        <v>-0.2188350847141507</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.2462903557589158</v>
+        <v>-0.2480058938364351</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.2414386360836573</v>
+        <v>-0.2431810445166036</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3647818879981628</v>
+        <v>-0.3667627546549284</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.4037799277490919</v>
+        <v>-0.4062548841324158</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.3602920261685725</v>
+        <v>-0.3634427265961762</v>
       </c>
     </row>
   </sheetData>
